--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Jarras" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jarras" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:13</t>
+          <t>Todas las regiones · Corte 11/09/2026 11:45</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -831,23 +831,23 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
         <v/>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -864,10 +864,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:13</t>
+          <t>Todas las regiones · Corte 11/09/2026 11:45</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -3485,21 +3485,21 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>7</v>
@@ -3525,37 +3525,37 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
         <v/>
       </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -3565,37 +3565,37 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
         <v>5</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
         <v/>
       </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:13</t>
+          <t>Todas las regiones · Corte 11/09/2026 11:45</t>
         </is>
       </c>
     </row>
@@ -16526,10 +16526,10 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E17" s="13">
         <f>IFERROR(C17/(C17+D17),0)</f>
@@ -16600,7 +16600,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:13</t>
+          <t>Todas las regiones · Corte 11/09/2026 11:45</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>437</v>
+        <v>575</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3829</v>
+        <v>3690</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -692,17 +692,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Nancy Rodriguez</t>
+          <t>Enrique César</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -725,17 +725,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Enrique César</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -758,17 +758,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Nancy Rodriguez</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -791,30 +791,30 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
         <v/>
       </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
         <v/>
       </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -864,10 +864,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1845,24 +1845,24 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
         <v>10</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1885,21 +1885,21 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>2</v>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>2</v>
@@ -1965,37 +1965,37 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2019,23 +2019,23 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2059,23 +2059,23 @@
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2085,37 +2085,37 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
         <v>9</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2125,37 +2125,37 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
         <v>9</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
         <v/>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2165,37 +2165,37 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
         <v/>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -2245,24 +2245,24 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -2365,24 +2365,24 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -2485,24 +2485,24 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -2525,24 +2525,24 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -2565,24 +2565,24 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -2645,24 +2645,24 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -2685,24 +2685,24 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -2725,24 +2725,24 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>5</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -2765,24 +2765,24 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2845,24 +2845,24 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -2885,24 +2885,24 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -2925,24 +2925,24 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2965,24 +2965,24 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>7</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -3005,24 +3005,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>7</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -3045,37 +3045,37 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
         <v/>
       </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3085,37 +3085,37 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
         <v/>
       </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3125,37 +3125,37 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
         <v/>
       </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3165,37 +3165,37 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
         <v/>
       </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3205,37 +3205,37 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
         <v/>
       </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3245,37 +3245,37 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
         <v/>
       </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3285,37 +3285,37 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
         <v/>
       </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3325,37 +3325,37 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
         <v/>
       </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3379,23 +3379,23 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
         <v/>
       </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3405,37 +3405,37 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
         <v/>
       </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3445,37 +3445,37 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
         <v/>
       </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3485,37 +3485,37 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G49" s="13">
         <f>IFERROR(E49/(E49+F49),0)</f>
         <v/>
       </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3539,23 +3539,23 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
         <v/>
       </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3565,37 +3565,37 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
         <v/>
       </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3605,37 +3605,37 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
         <v/>
       </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3645,37 +3645,37 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
         <v/>
       </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I53" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3699,23 +3699,23 @@
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
         <v/>
       </c>
-      <c r="H54" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I54" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3725,37 +3725,37 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
         <v/>
       </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3765,37 +3765,37 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
         <v/>
       </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3805,37 +3805,37 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
         <v/>
       </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3845,37 +3845,37 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
         <v/>
       </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3885,37 +3885,37 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G59" s="13">
         <f>IFERROR(E59/(E59+F59),0)</f>
         <v/>
       </c>
-      <c r="H59" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I59" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3925,37 +3925,37 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
         <v/>
       </c>
-      <c r="H60" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I60" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3965,37 +3965,37 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G61" s="13">
         <f>IFERROR(E61/(E61+F61),0)</f>
         <v/>
       </c>
-      <c r="H61" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -4005,37 +4005,37 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G62" s="9">
         <f>IFERROR(E62/(E62+F62),0)</f>
         <v/>
       </c>
-      <c r="H62" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I62" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -4045,37 +4045,37 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G63" s="13">
         <f>IFERROR(E63/(E63+F63),0)</f>
         <v/>
       </c>
-      <c r="H63" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I63" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G64" s="9">
         <f>IFERROR(E64/(E64+F64),0)</f>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G65" s="13">
         <f>IFERROR(E65/(E65+F65),0)</f>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="E66" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G66" s="9">
         <f>IFERROR(E66/(E66+F66),0)</f>
@@ -4205,24 +4205,24 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G67" s="13">
         <f>IFERROR(E67/(E67+F67),0)</f>
@@ -4245,24 +4245,24 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G68" s="9">
         <f>IFERROR(E68/(E68+F68),0)</f>
@@ -4285,24 +4285,24 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G69" s="13">
         <f>IFERROR(E69/(E69+F69),0)</f>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="E70" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G70" s="9">
         <f>IFERROR(E70/(E70+F70),0)</f>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="E71" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G71" s="13">
         <f>IFERROR(E71/(E71+F71),0)</f>
@@ -4405,24 +4405,24 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G72" s="9">
         <f>IFERROR(E72/(E72+F72),0)</f>
@@ -4445,24 +4445,24 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G73" s="13">
         <f>IFERROR(E73/(E73+F73),0)</f>
@@ -4485,24 +4485,24 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G74" s="9">
         <f>IFERROR(E74/(E74+F74),0)</f>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -4539,10 +4539,10 @@
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G76" s="9">
         <f>IFERROR(E76/(E76+F76),0)</f>
@@ -4605,24 +4605,24 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G77" s="13">
         <f>IFERROR(E77/(E77+F77),0)</f>
@@ -4645,24 +4645,24 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G78" s="9">
         <f>IFERROR(E78/(E78+F78),0)</f>
@@ -4685,24 +4685,24 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G79" s="13">
         <f>IFERROR(E79/(E79+F79),0)</f>
@@ -4725,24 +4725,24 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G80" s="9">
         <f>IFERROR(E80/(E80+F80),0)</f>
@@ -4765,24 +4765,24 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G81" s="13">
         <f>IFERROR(E81/(E81+F81),0)</f>
@@ -4805,17 +4805,17 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5165,17 +5165,17 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -6965,17 +6965,17 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -7045,17 +7045,17 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -7085,17 +7085,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7125,17 +7125,17 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -7285,17 +7285,17 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -7445,17 +7445,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7765,17 +7765,17 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7885,17 +7885,17 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
@@ -8485,24 +8485,24 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G174" s="9">
         <f>IFERROR(E174/(E174+F174),0)</f>
@@ -8525,24 +8525,24 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G175" s="13">
         <f>IFERROR(E175/(E175+F175),0)</f>
@@ -8565,17 +8565,17 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
@@ -8605,17 +8605,17 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E177" s="11" t="n">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9005,17 +9005,17 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9045,17 +9045,17 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
@@ -9085,17 +9085,17 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E190" s="7" t="n">
@@ -9165,17 +9165,17 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
@@ -9285,17 +9285,17 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E194" s="7" t="n">
@@ -9325,17 +9325,17 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9445,17 +9445,17 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9565,17 +9565,17 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9845,12 +9845,12 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
@@ -9965,17 +9965,17 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Ciudad Jardin ll</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Coapa Chedraui</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -10045,17 +10045,17 @@
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Condesa</t>
+          <t>Ciudad Jardin ll</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Copilco 20</t>
+          <t>Coapa Chedraui</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E214" s="7" t="n">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Coyoacan</t>
+          <t>Condesa</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
@@ -10165,17 +10165,17 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Corporativo HSBC</t>
+          <t>Copilco 20</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Polanco</t>
+          <t>Corporativo Coyoacan</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
@@ -10245,17 +10245,17 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>Coyoacan Centro</t>
+          <t>Corporativo HSBC</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
@@ -10285,17 +10285,17 @@
       </c>
       <c r="B219" s="15" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>Division del Norte</t>
+          <t>Corporativo Polanco</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E219" s="11" t="n">
@@ -10325,17 +10325,17 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Division del Norte II</t>
+          <t>Coyoacan Centro</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
@@ -10365,17 +10365,17 @@
       </c>
       <c r="B221" s="15" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>Ejercito Nacional</t>
+          <t>Division del Norte</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
@@ -10405,17 +10405,17 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>Embassy Suites</t>
+          <t>Division del Norte II</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
@@ -10445,17 +10445,17 @@
       </c>
       <c r="B223" s="15" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Ejercito Nacional</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
@@ -10485,17 +10485,17 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Embassy Suites</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
@@ -10525,17 +10525,17 @@
       </c>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Fiesta Americana Reforma</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E225" s="11" t="n">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Forum Buenavista</t>
+          <t>Fiesta Americana Reforma</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
@@ -10605,12 +10605,12 @@
       </c>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Forum Buenavista II</t>
+          <t>Forum Buenavista</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
@@ -10645,17 +10645,17 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Galerias Coapa</t>
+          <t>Forum Buenavista II</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
@@ -10685,17 +10685,17 @@
       </c>
       <c r="B229" s="15" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Galerias metepec 1</t>
+          <t>Galerias Coapa</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
@@ -10725,17 +10725,17 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Galerias metepec 1</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
@@ -10765,17 +10765,17 @@
       </c>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Gran Sur</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Grand San Jeronimo</t>
+          <t>Gran Sur</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
@@ -10845,17 +10845,17 @@
       </c>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Homero</t>
+          <t>Grand San Jeronimo</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E233" s="11" t="n">
@@ -10885,17 +10885,17 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles Clinica Londres</t>
+          <t>Homero</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="B235" s="15" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles Metropolitano</t>
+          <t>Hospital Angeles Clinica Londres</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
@@ -10965,17 +10965,17 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal</t>
+          <t>Hospital Angeles Metropolitano</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="B237" s="15" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal II</t>
+          <t>Hospital Angeles del Pedregal</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
@@ -11045,17 +11045,17 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Relox</t>
+          <t>Hospital Angeles del Pedregal II</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
@@ -11085,17 +11085,17 @@
       </c>
       <c r="B239" s="15" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Tehuantepec</t>
+          <t>Insurgentes Relox</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
@@ -11125,17 +11125,17 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Wtc</t>
+          <t>Insurgentes Tehuantepec</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
@@ -11165,17 +11165,17 @@
       </c>
       <c r="B241" s="15" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Insurgentes Wtc</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
@@ -11205,17 +11205,17 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Irrigacion</t>
+          <t>Interlomas</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E242" s="7" t="n">
@@ -11245,17 +11245,17 @@
       </c>
       <c r="B243" s="15" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38219</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Jardines del Pedregal</t>
+          <t>Irrigacion</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Jolie Place</t>
+          <t>Jardines del Pedregal</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
@@ -11325,17 +11325,17 @@
       </c>
       <c r="B245" s="15" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>Juan Pablo II</t>
+          <t>Jolie Place</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E245" s="11" t="n">
@@ -11365,17 +11365,17 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>Juarez 32</t>
+          <t>Juan Pablo II</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
@@ -11405,17 +11405,17 @@
       </c>
       <c r="B247" s="15" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Juarez 32</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
@@ -11445,17 +11445,17 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>La Salle</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
@@ -11485,17 +11485,17 @@
       </c>
       <c r="B249" s="15" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Macroplaza Tecamac</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
@@ -11525,17 +11525,17 @@
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Madero</t>
+          <t>Macroplaza Tecamac</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B251" s="15" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>Masarik</t>
+          <t>Madero</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Masarik Spencer</t>
+          <t>Masarik</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
@@ -11645,17 +11645,17 @@
       </c>
       <c r="B253" s="15" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>Medica Sur</t>
+          <t>Masarik Spencer</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
@@ -11685,17 +11685,17 @@
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Mexfund Pedregal</t>
+          <t>Medica Sur</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
@@ -11725,17 +11725,17 @@
       </c>
       <c r="B255" s="15" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo II</t>
+          <t>Mexfund Pedregal</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E255" s="11" t="n">
@@ -11765,12 +11765,12 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo III</t>
+          <t>Miguel Angel de Quevedo II</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
@@ -11805,17 +11805,17 @@
       </c>
       <c r="B257" s="15" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>Miramontes</t>
+          <t>Miguel Angel de Quevedo III</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
@@ -11845,17 +11845,17 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>Mitikah</t>
+          <t>Miramontes</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="B259" s="15" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>Mitikah Restaurantes</t>
+          <t>Mitikah</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
@@ -11925,17 +11925,17 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Miyana</t>
+          <t>Mitikah Restaurantes</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="B261" s="15" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>Miyana II</t>
+          <t>Miyana</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
@@ -12005,17 +12005,17 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Moliere 222</t>
+          <t>Miyana II</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>Montecitos Wtc</t>
+          <t>Moliere 222</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
@@ -12085,17 +12085,17 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Multiplaza Bosques</t>
+          <t>Montecitos Wtc</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
@@ -12125,17 +12125,17 @@
       </c>
       <c r="B265" s="15" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>Oasis I</t>
+          <t>Multiplaza Bosques</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
@@ -12165,12 +12165,12 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>Oasis II</t>
+          <t>Oasis I</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
@@ -12205,17 +12205,17 @@
       </c>
       <c r="B267" s="15" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>Obelisco</t>
+          <t>Oasis II</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E267" s="11" t="n">
@@ -12245,17 +12245,17 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>Obrero Mundial</t>
+          <t>Obelisco</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
@@ -12285,17 +12285,17 @@
       </c>
       <c r="B269" s="15" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Cuemanco</t>
+          <t>Obrero Mundial</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
@@ -12325,17 +12325,17 @@
       </c>
       <c r="B270" s="17" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>Parques BBVA</t>
+          <t>Pabellon Cuemanco</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="B271" s="15" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>Parques Polanco</t>
+          <t>Parques BBVA</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
@@ -12405,17 +12405,17 @@
       </c>
       <c r="B272" s="17" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Pasaje San Jeronimo</t>
+          <t>Parques Polanco</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
@@ -12445,17 +12445,17 @@
       </c>
       <c r="B273" s="15" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>Paseo Ventura</t>
+          <t>Pasaje San Jeronimo</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E273" s="11" t="n">
@@ -12485,17 +12485,17 @@
       </c>
       <c r="B274" s="17" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Patio Boturini</t>
+          <t>Paseo Ventura</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
@@ -12525,17 +12525,17 @@
       </c>
       <c r="B275" s="15" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>Patio Lomas Estrella</t>
+          <t>Patio Boturini</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
@@ -12565,17 +12565,17 @@
       </c>
       <c r="B276" s="17" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Patio Revolución</t>
+          <t>Patio Lomas Estrella</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -12605,17 +12605,17 @@
       </c>
       <c r="B277" s="15" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>Patio Tlalpan</t>
+          <t>Patio Revolución</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E277" s="11" t="n">
@@ -12645,17 +12645,17 @@
       </c>
       <c r="B278" s="17" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Patio Universidad</t>
+          <t>Patio Tlalpan</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
@@ -12685,17 +12685,17 @@
       </c>
       <c r="B279" s="15" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>Pedregal</t>
+          <t>Patio Universidad</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E279" s="11" t="n">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="B280" s="17" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>PeriSur</t>
+          <t>Pedregal</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
@@ -12765,17 +12765,17 @@
       </c>
       <c r="B281" s="15" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>Periferico Polanco DT</t>
+          <t>PeriSur</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
@@ -12805,17 +12805,17 @@
       </c>
       <c r="B282" s="17" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>Perisur Reserve</t>
+          <t>Periferico Polanco DT</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
@@ -12845,17 +12845,17 @@
       </c>
       <c r="B283" s="15" t="inlineStr">
         <is>
-          <t>38482</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>Pestalozzi</t>
+          <t>Perisur Reserve</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
@@ -12885,17 +12885,17 @@
       </c>
       <c r="B284" s="17" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>Picacho Ajusco</t>
+          <t>Pestalozzi</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
@@ -12925,17 +12925,17 @@
       </c>
       <c r="B285" s="15" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>Pilares</t>
+          <t>Picacho Ajusco</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
@@ -12965,17 +12965,17 @@
       </c>
       <c r="B286" s="17" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>Plaza Alameda</t>
+          <t>Pilares</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
@@ -13005,17 +13005,17 @@
       </c>
       <c r="B287" s="15" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>Plaza America DT</t>
+          <t>Plaza Alameda</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
@@ -13045,17 +13045,17 @@
       </c>
       <c r="B288" s="17" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aragon</t>
+          <t>Plaza America DT</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
@@ -13085,17 +13085,17 @@
       </c>
       <c r="B289" s="15" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>Plaza Basica</t>
+          <t>Plaza Aragon</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
@@ -13125,12 +13125,12 @@
       </c>
       <c r="B290" s="17" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Plaza Central</t>
+          <t>Plaza Basica</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
@@ -13165,17 +13165,17 @@
       </c>
       <c r="B291" s="15" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>Plaza Chimalhuacan</t>
+          <t>Plaza Central</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E291" s="11" t="n">
@@ -13205,17 +13205,17 @@
       </c>
       <c r="B292" s="17" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Plaza Cuicuilco</t>
+          <t>Plaza Chimalhuacan</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
@@ -13245,17 +13245,17 @@
       </c>
       <c r="B293" s="15" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Alta</t>
+          <t>Plaza Cuicuilco</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E293" s="11" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="B294" s="17" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38173</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Baja</t>
+          <t>Plaza Delta Planta Alta</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
@@ -13325,17 +13325,17 @@
       </c>
       <c r="B295" s="15" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>Plaza Ermita</t>
+          <t>Plaza Delta Planta Baja</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E295" s="11" t="n">
@@ -13365,17 +13365,17 @@
       </c>
       <c r="B296" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Ermita</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16176,10 +16176,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16211,10 +16211,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -16246,10 +16246,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -16281,10 +16281,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16316,10 +16316,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16386,10 +16386,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$361</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$112</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jarras'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:24</t>
+          <t>Todas las regiones · Corte 14/09/2026 16:59</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3690</v>
+        <v>3666</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -692,17 +692,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Enrique César</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -725,17 +725,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Enrique César</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -897,10 +897,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(D16/(D16+E16),0)</f>
@@ -930,10 +930,10 @@
         <v>8</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F17" s="13">
         <f>IFERROR(D17/(D17+E17),0)</f>
@@ -956,17 +956,17 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Adriana Tanus</t>
+          <t>Jose Magos</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(D18/(D18+E18),0)</f>
@@ -989,17 +989,17 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Areli Lazcano</t>
+          <t>Daniel Flores</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F19" s="13">
         <f>IFERROR(D19/(D19+E19),0)</f>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Erika Contreras</t>
+          <t>Adriana Tanus</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(D20/(D20+E20),0)</f>
@@ -1055,17 +1055,17 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Jose Magos</t>
+          <t>Erika Contreras</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F21" s="13">
         <f>IFERROR(D21/(D21+E21),0)</f>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores</t>
+          <t>Areli Lazcano</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(D22/(D22+E22),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:24</t>
+          <t>Todas las regiones · Corte 14/09/2026 16:59</t>
         </is>
       </c>
     </row>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1765,24 +1765,24 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>1</v>
@@ -1885,24 +1885,24 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
         <v>10</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1925,24 +1925,24 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
         <v>10</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1965,17 +1965,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>2</v>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>2</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2205,37 +2205,37 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
         <v>9</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
         <v/>
       </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2245,37 +2245,37 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
         <v>9</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
         <v/>
       </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2285,17 +2285,17 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -2405,21 +2405,21 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>3</v>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -2525,17 +2525,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2645,17 +2645,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2885,21 +2885,21 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>4</v>
@@ -2925,17 +2925,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2965,24 +2965,24 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
         <v>7</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -3005,17 +3005,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -4565,24 +4565,24 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G76" s="9">
         <f>IFERROR(E76/(E76+F76),0)</f>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G77" s="13">
         <f>IFERROR(E77/(E77+F77),0)</f>
@@ -4645,24 +4645,24 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G78" s="9">
         <f>IFERROR(E78/(E78+F78),0)</f>
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -4805,24 +4805,24 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G82" s="9">
         <f>IFERROR(E82/(E82+F82),0)</f>
@@ -4845,24 +4845,24 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G83" s="13">
         <f>IFERROR(E83/(E83+F83),0)</f>
@@ -4885,24 +4885,24 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G84" s="9">
         <f>IFERROR(E84/(E84+F84),0)</f>
@@ -4925,24 +4925,24 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G85" s="13">
         <f>IFERROR(E85/(E85+F85),0)</f>
@@ -4965,24 +4965,24 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G86" s="9">
         <f>IFERROR(E86/(E86+F86),0)</f>
@@ -5005,24 +5005,24 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G87" s="13">
         <f>IFERROR(E87/(E87+F87),0)</f>
@@ -5045,24 +5045,24 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G88" s="9">
         <f>IFERROR(E88/(E88+F88),0)</f>
@@ -5085,24 +5085,24 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G89" s="13">
         <f>IFERROR(E89/(E89+F89),0)</f>
@@ -5125,24 +5125,24 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G90" s="9">
         <f>IFERROR(E90/(E90+F90),0)</f>
@@ -5165,24 +5165,24 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G91" s="13">
         <f>IFERROR(E91/(E91+F91),0)</f>
@@ -5205,24 +5205,24 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G92" s="9">
         <f>IFERROR(E92/(E92+F92),0)</f>
@@ -5245,12 +5245,12 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="E93" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G93" s="13">
         <f>IFERROR(E93/(E93+F93),0)</f>
@@ -5285,24 +5285,24 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G94" s="9">
         <f>IFERROR(E94/(E94+F94),0)</f>
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -6965,17 +6965,17 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -7045,17 +7045,17 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -7085,17 +7085,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7125,17 +7125,17 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:24</t>
+          <t>Todas las regiones · Corte 14/09/2026 16:59</t>
         </is>
       </c>
     </row>
@@ -16316,10 +16316,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="E16" s="9">
         <f>IFERROR(C16/(C16+D16),0)</f>
@@ -16542,7 +16542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16565,7 +16565,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 13/09/2026 18:24</t>
+          <t>Todas las regiones · Corte 14/09/2026 16:59</t>
         </is>
       </c>
     </row>
@@ -16716,17 +16716,17 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17889997091362912024305341934699_Ramon%20Espinosa%20Macia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894098786624170437606810729851_Ramon%20Espinosa%20Macia.jpg</t>
         </is>
       </c>
     </row>
@@ -16764,17 +16764,17 @@
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -16788,50 +16788,50 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
         </is>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -16850,19 +16850,19 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -16871,122 +16871,122 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -16995,29 +16995,29 @@
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -17036,19 +17036,19 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -17057,29 +17057,29 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -17091,26 +17091,26 @@
         <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -17119,29 +17119,29 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
         </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -17160,19 +17160,19 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -17181,29 +17181,29 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -17212,29 +17212,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -17243,96 +17243,96 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
@@ -17346,19 +17346,19 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -17367,29 +17367,29 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -17398,29 +17398,29 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -17429,29 +17429,29 @@
         </is>
       </c>
       <c r="D31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -17460,29 +17460,29 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -17491,34 +17491,34 @@
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
@@ -17532,81 +17532,81 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -17625,19 +17625,19 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -17646,29 +17646,29 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -17677,29 +17677,29 @@
         </is>
       </c>
       <c r="D39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -17718,19 +17718,19 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -17739,29 +17739,29 @@
         </is>
       </c>
       <c r="D41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -17780,19 +17780,19 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
         </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -17811,19 +17811,19 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -17842,19 +17842,19 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -17866,31 +17866,31 @@
         <v>2</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
@@ -17904,55 +17904,55 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
@@ -17966,19 +17966,19 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -17987,29 +17987,29 @@
         </is>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -18028,19 +18028,19 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -18052,26 +18052,26 @@
         <v>2</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -18090,19 +18090,19 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -18114,26 +18114,26 @@
         <v>1</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -18142,29 +18142,29 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -18173,29 +18173,29 @@
         </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -18207,31 +18207,31 @@
         <v>1</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="D57" s="11" t="n">
@@ -18245,81 +18245,81 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
         </is>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -18338,19 +18338,19 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -18362,26 +18362,26 @@
         <v>2</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -18390,29 +18390,29 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -18421,29 +18421,29 @@
         </is>
       </c>
       <c r="D63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -18462,19 +18462,19 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -18493,19 +18493,19 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
         </is>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -18514,29 +18514,29 @@
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -18545,29 +18545,29 @@
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -18586,19 +18586,19 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -18617,19 +18617,19 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
         </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -18641,26 +18641,26 @@
         <v>1</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -18669,122 +18669,122 @@
         </is>
       </c>
       <c r="D71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E71" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
         </is>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="D72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
         </is>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
         </is>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -18793,29 +18793,29 @@
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -18827,26 +18827,26 @@
         <v>2</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -18855,29 +18855,29 @@
         </is>
       </c>
       <c r="D77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
         </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
       <c r="A78" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -18896,19 +18896,19 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
         </is>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -18920,26 +18920,26 @@
         <v>2</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
         </is>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -18948,29 +18948,29 @@
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -18989,19 +18989,19 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
         </is>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -19010,29 +19010,29 @@
         </is>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
         </is>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -19041,29 +19041,29 @@
         </is>
       </c>
       <c r="D83" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E83" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
         </is>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -19082,19 +19082,19 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
         </is>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -19103,29 +19103,29 @@
         </is>
       </c>
       <c r="D85" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -19134,96 +19134,96 @@
         </is>
       </c>
       <c r="D86" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="D87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>5</v>
-      </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
         </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="D88" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
         </is>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="D89" s="11" t="n">
@@ -19237,19 +19237,19 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
         </is>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -19258,29 +19258,29 @@
         </is>
       </c>
       <c r="D90" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="F90" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
         </is>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -19299,19 +19299,19 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
         </is>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -19330,19 +19330,19 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
         </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -19351,29 +19351,29 @@
         </is>
       </c>
       <c r="D93" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
         </is>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -19382,29 +19382,29 @@
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
         </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -19423,19 +19423,19 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -19447,119 +19447,119 @@
         <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="D97" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="D98" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
         </is>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -19568,29 +19568,29 @@
         </is>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
         </is>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -19609,19 +19609,19 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -19630,29 +19630,29 @@
         </is>
       </c>
       <c r="D102" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
         </is>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -19664,26 +19664,26 @@
         <v>2</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
         </is>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
@@ -19695,26 +19695,26 @@
         <v>1</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
         </is>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -19723,29 +19723,29 @@
         </is>
       </c>
       <c r="D105" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E105" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
         </is>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -19764,19 +19764,19 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
         </is>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -19785,29 +19785,29 @@
         </is>
       </c>
       <c r="D107" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
         </is>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -19816,29 +19816,29 @@
         </is>
       </c>
       <c r="D108" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
         </is>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -19857,34 +19857,127 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="21" customHeight="1">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>38722</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Patio Barranca N2</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="21" customHeight="1">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>38720</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Patio Barranca PB</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="21" customHeight="1">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>38644</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Torre Virreyes</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
           <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891464434056746458223120183687_Starbucks%20Torre%20Virr.jpg</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="21" customHeight="1">
-      <c r="A110" s="18" t="n"/>
-      <c r="B110" s="19" t="n"/>
-      <c r="C110" s="19" t="inlineStr">
+    <row r="113" ht="21" customHeight="1">
+      <c r="A113" s="18" t="n"/>
+      <c r="B113" s="19" t="n"/>
+      <c r="C113" s="19" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
       </c>
-      <c r="D110" s="20">
-        <f>SUM(D5:D109)</f>
-        <v/>
-      </c>
-      <c r="E110" s="20">
-        <f>SUM(E5:E109)</f>
-        <v/>
-      </c>
-      <c r="F110" s="20">
-        <f>SUM(F5:F109)</f>
-        <v/>
-      </c>
-      <c r="G110" s="19" t="n"/>
+      <c r="D113" s="20">
+        <f>SUM(D5:D112)</f>
+        <v/>
+      </c>
+      <c r="E113" s="20">
+        <f>SUM(E5:E112)</f>
+        <v/>
+      </c>
+      <c r="F113" s="20">
+        <f>SUM(F5:F112)</f>
+        <v/>
+      </c>
+      <c r="G113" s="19" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G109"/>
+  <autoFilter ref="A4:G112"/>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:G2"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -923,17 +923,17 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava</t>
+          <t>Jose Magos</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="F17" s="13">
         <f>IFERROR(D17/(D17+E17),0)</f>
@@ -956,17 +956,17 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Jose Magos</t>
+          <t>Andrea Nava</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(D18/(D18+E18),0)</f>
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5165,17 +5165,17 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -5205,17 +5205,17 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -5325,24 +5325,24 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G95" s="13">
         <f>IFERROR(E95/(E95+F95),0)</f>
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E16" s="9">
         <f>IFERROR(C16/(C16+D16),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 09:28</t>
+          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3608</v>
+        <v>3603</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -956,7 +956,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores</t>
+          <t>Areli Lazcano</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -989,17 +989,17 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava</t>
+          <t>Daniel Flores</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="F19" s="13">
         <f>IFERROR(D19/(D19+E19),0)</f>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Areli Lazcano</t>
+          <t>Andrea Nava</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D20" s="7" t="n">
-        <v>19</v>
-      </c>
       <c r="E20" s="8" t="n">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(D20/(D20+E20),0)</f>
@@ -1062,10 +1062,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F21" s="13">
         <f>IFERROR(D21/(D21+E21),0)</f>
@@ -1128,10 +1128,10 @@
         <v>11</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F23" s="13">
         <f>IFERROR(D23/(D23+E23),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 09:28</t>
+          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
         </is>
       </c>
     </row>
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -4725,24 +4725,24 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G80" s="9">
         <f>IFERROR(E80/(E80+F80),0)</f>
@@ -4765,24 +4765,24 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G81" s="13">
         <f>IFERROR(E81/(E81+F81),0)</f>
@@ -4805,12 +4805,12 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,24 +6885,24 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G134" s="9">
         <f>IFERROR(E134/(E134+F134),0)</f>
@@ -6925,24 +6925,24 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G135" s="13">
         <f>IFERROR(E135/(E135+F135),0)</f>
@@ -6965,24 +6965,24 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G136" s="9">
         <f>IFERROR(E136/(E136+F136),0)</f>
@@ -7005,24 +7005,24 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G137" s="13">
         <f>IFERROR(E137/(E137+F137),0)</f>
@@ -7045,17 +7045,17 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -7085,17 +7085,17 @@
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7125,17 +7125,17 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -7285,17 +7285,17 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -7445,17 +7445,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Galerias metepec 1</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Galerias metepec 1</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
@@ -7805,17 +7805,17 @@
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7885,17 +7885,17 @@
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="16" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="B165" s="16" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="16" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 09:28</t>
+          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
         </is>
       </c>
     </row>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E16" s="9">
         <f>IFERROR(C16/(C16+D16),0)</f>
@@ -16565,7 +16565,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 09:28</t>
+          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
+          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3603</v>
+        <v>3590</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -923,7 +923,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Jose Magos</t>
+          <t>Erika Contreras</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -956,17 +956,17 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Areli Lazcano</t>
+          <t>Jose Magos</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(D18/(D18+E18),0)</f>
@@ -989,17 +989,17 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores</t>
+          <t>Areli Lazcano</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F19" s="13">
         <f>IFERROR(D19/(D19+E19),0)</f>
@@ -1029,10 +1029,10 @@
         <v>8</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(D20/(D20+E20),0)</f>
@@ -1055,17 +1055,17 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Erika Contreras</t>
+          <t>Daniel Flores</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="F21" s="13">
         <f>IFERROR(D21/(D21+E21),0)</f>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Adriana Tanus</t>
+          <t>Juan Zuñiga</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(D22/(D22+E22),0)</f>
@@ -1121,17 +1121,17 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Juan Zuñiga</t>
+          <t>Adriana Tanus</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F23" s="13">
         <f>IFERROR(D23/(D23+E23),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
+          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5205,17 +5205,17 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="16" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="B119" s="16" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -7045,24 +7045,24 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G138" s="9">
         <f>IFERROR(E138/(E138+F138),0)</f>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="E139" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G139" s="13">
         <f>IFERROR(E139/(E139+F139),0)</f>
@@ -7125,24 +7125,24 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G140" s="9">
         <f>IFERROR(E140/(E140+F140),0)</f>
@@ -7165,24 +7165,24 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G141" s="13">
         <f>IFERROR(E141/(E141+F141),0)</f>
@@ -7205,24 +7205,24 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G142" s="9">
         <f>IFERROR(E142/(E142+F142),0)</f>
@@ -7245,24 +7245,24 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G143" s="13">
         <f>IFERROR(E143/(E143+F143),0)</f>
@@ -7285,12 +7285,12 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="E144" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G144" s="9">
         <f>IFERROR(E144/(E144+F144),0)</f>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G145" s="13">
         <f>IFERROR(E145/(E145+F145),0)</f>
@@ -7365,24 +7365,24 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G146" s="9">
         <f>IFERROR(E146/(E146+F146),0)</f>
@@ -7405,24 +7405,24 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G147" s="13">
         <f>IFERROR(E147/(E147+F147),0)</f>
@@ -7445,24 +7445,24 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G148" s="9">
         <f>IFERROR(E148/(E148+F148),0)</f>
@@ -7485,24 +7485,24 @@
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G149" s="13">
         <f>IFERROR(E149/(E149+F149),0)</f>
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Galerias metepec 1</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7765,17 +7765,17 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7805,17 +7805,17 @@
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7885,17 +7885,17 @@
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Galerias metepec 1</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="16" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="16" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="16" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8445,17 +8445,17 @@
       </c>
       <c r="B173" s="16" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
@@ -8485,17 +8485,17 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="B175" s="16" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Star Medica Napoles</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
@@ -8565,17 +8565,17 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
@@ -8605,24 +8605,24 @@
       </c>
       <c r="B177" s="16" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E177" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G177" s="13">
         <f>IFERROR(E177/(E177+F177),0)</f>
@@ -8645,12 +8645,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
@@ -8685,17 +8685,17 @@
       </c>
       <c r="B179" s="16" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E179" s="11" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="B181" s="16" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="B183" s="16" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="16" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9005,17 +9005,17 @@
       </c>
       <c r="B187" s="16" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9045,17 +9045,17 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
@@ -9085,17 +9085,17 @@
       </c>
       <c r="B189" s="16" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
@@ -9165,17 +9165,17 @@
       </c>
       <c r="B191" s="16" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="B193" s="16" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="B195" s="16" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B197" s="16" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="B199" s="16" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9565,17 +9565,17 @@
       </c>
       <c r="B201" s="16" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="B203" s="16" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B205" s="16" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B207" s="16" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9845,17 +9845,17 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="B209" s="16" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
@@ -9965,17 +9965,17 @@
       </c>
       <c r="B211" s="16" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -10045,17 +10045,17 @@
       </c>
       <c r="B213" s="16" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
@@ -10085,12 +10085,12 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin ll</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="B215" s="16" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>Coapa Chedraui</t>
+          <t>Ciudad Jardin ll</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
@@ -10165,17 +10165,17 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Condesa</t>
+          <t>Coapa Chedraui</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="B217" s="16" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Copilco 20</t>
+          <t>Condesa</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
@@ -10245,17 +10245,17 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Coyoacan</t>
+          <t>Copilco 20</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
@@ -10285,17 +10285,17 @@
       </c>
       <c r="B219" s="16" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>Corporativo HSBC</t>
+          <t>Corporativo Coyoacan</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E219" s="11" t="n">
@@ -10325,17 +10325,17 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Polanco</t>
+          <t>Corporativo HSBC</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
@@ -10365,17 +10365,17 @@
       </c>
       <c r="B221" s="16" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>Coyoacan Centro</t>
+          <t>Corporativo Polanco</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
@@ -10405,17 +10405,17 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>Division del Norte</t>
+          <t>Coyoacan Centro</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="B223" s="16" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Division del Norte II</t>
+          <t>Division del Norte</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
@@ -10485,17 +10485,17 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>Ejercito Nacional</t>
+          <t>Division del Norte II</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
@@ -10525,17 +10525,17 @@
       </c>
       <c r="B225" s="16" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Embassy Suites</t>
+          <t>Ejercito Nacional</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E225" s="11" t="n">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Embassy Suites</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
@@ -10605,17 +10605,17 @@
       </c>
       <c r="B227" s="16" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Fiesta Americana Reforma</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
@@ -10645,17 +10645,17 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Forum Buenavista</t>
+          <t>Fiesta Americana Reforma</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="B229" s="16" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Forum Buenavista II</t>
+          <t>Forum Buenavista</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
@@ -10725,17 +10725,17 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Galerias Coapa</t>
+          <t>Forum Buenavista II</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
@@ -10765,17 +10765,17 @@
       </c>
       <c r="B231" s="16" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Galerias Coapa</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Gran Sur</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
@@ -10845,17 +10845,17 @@
       </c>
       <c r="B233" s="16" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Grand San Jeronimo</t>
+          <t>Gran Sur</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E233" s="11" t="n">
@@ -10885,17 +10885,17 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Homero</t>
+          <t>Grand San Jeronimo</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
@@ -10925,17 +10925,17 @@
       </c>
       <c r="B235" s="16" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles Clinica Londres</t>
+          <t>Homero</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E235" s="11" t="n">
@@ -10965,12 +10965,12 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles Metropolitano</t>
+          <t>Hospital Angeles Clinica Londres</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="B237" s="16" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal</t>
+          <t>Hospital Angeles Metropolitano</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal II</t>
+          <t>Hospital Angeles del Pedregal</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
@@ -11085,17 +11085,17 @@
       </c>
       <c r="B239" s="16" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Relox</t>
+          <t>Hospital Angeles del Pedregal II</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
@@ -11125,17 +11125,17 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Tehuantepec</t>
+          <t>Insurgentes Relox</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
@@ -11165,17 +11165,17 @@
       </c>
       <c r="B241" s="16" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Wtc</t>
+          <t>Insurgentes Tehuantepec</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
@@ -11205,17 +11205,17 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Insurgentes Wtc</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E242" s="7" t="n">
@@ -11245,17 +11245,17 @@
       </c>
       <c r="B243" s="16" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Irrigacion</t>
+          <t>Interlomas</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
@@ -11285,17 +11285,17 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38219</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Jardines del Pedregal</t>
+          <t>Irrigacion</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="B245" s="16" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>Jolie Place</t>
+          <t>Jardines del Pedregal</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
@@ -11365,17 +11365,17 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>Juan Pablo II</t>
+          <t>Jolie Place</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
@@ -11405,17 +11405,17 @@
       </c>
       <c r="B247" s="16" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>Juarez 32</t>
+          <t>Juan Pablo II</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
@@ -11445,17 +11445,17 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Juarez 32</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
@@ -11485,17 +11485,17 @@
       </c>
       <c r="B249" s="16" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>La Salle</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
@@ -11525,17 +11525,17 @@
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Macroplaza Tecamac</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B251" s="16" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>Madero</t>
+          <t>Macroplaza Tecamac</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Masarik</t>
+          <t>Madero</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
@@ -11645,17 +11645,17 @@
       </c>
       <c r="B253" s="16" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>Masarik Spencer</t>
+          <t>Masarik</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
@@ -11685,17 +11685,17 @@
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Medica Sur</t>
+          <t>Masarik Spencer</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
@@ -11725,17 +11725,17 @@
       </c>
       <c r="B255" s="16" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>Mexfund Pedregal</t>
+          <t>Medica Sur</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E255" s="11" t="n">
@@ -11765,17 +11765,17 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo II</t>
+          <t>Mexfund Pedregal</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="B257" s="16" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo III</t>
+          <t>Miguel Angel de Quevedo II</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
@@ -11845,17 +11845,17 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>Miramontes</t>
+          <t>Miguel Angel de Quevedo III</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
@@ -11885,17 +11885,17 @@
       </c>
       <c r="B259" s="16" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>Mitikah</t>
+          <t>Miramontes</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E259" s="11" t="n">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Mitikah Restaurantes</t>
+          <t>Mitikah</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="B261" s="16" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>Miyana</t>
+          <t>Mitikah Restaurantes</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E261" s="11" t="n">
@@ -12005,12 +12005,12 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Miyana II</t>
+          <t>Miyana</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B263" s="16" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>Moliere 222</t>
+          <t>Miyana II</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
@@ -12085,17 +12085,17 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Montecitos Wtc</t>
+          <t>Moliere 222</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
@@ -12125,17 +12125,17 @@
       </c>
       <c r="B265" s="16" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>Multiplaza Bosques</t>
+          <t>Montecitos Wtc</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
@@ -12165,17 +12165,17 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>Oasis I</t>
+          <t>Multiplaza Bosques</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="B267" s="16" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>Oasis II</t>
+          <t>Oasis I</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
@@ -12245,17 +12245,17 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>Obelisco</t>
+          <t>Oasis II</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
@@ -12285,17 +12285,17 @@
       </c>
       <c r="B269" s="16" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>Obrero Mundial</t>
+          <t>Obelisco</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
@@ -12325,17 +12325,17 @@
       </c>
       <c r="B270" s="17" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Cuemanco</t>
+          <t>Obrero Mundial</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="B271" s="16" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>Parques BBVA</t>
+          <t>Pabellon Cuemanco</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
@@ -12405,17 +12405,17 @@
       </c>
       <c r="B272" s="17" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Parques Polanco</t>
+          <t>Parques BBVA</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
@@ -12445,17 +12445,17 @@
       </c>
       <c r="B273" s="16" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>Pasaje San Jeronimo</t>
+          <t>Parques Polanco</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E273" s="11" t="n">
@@ -12485,17 +12485,17 @@
       </c>
       <c r="B274" s="17" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Paseo Ventura</t>
+          <t>Pasaje San Jeronimo</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
@@ -12525,17 +12525,17 @@
       </c>
       <c r="B275" s="16" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>Patio Boturini</t>
+          <t>Paseo Ventura</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
@@ -12565,17 +12565,17 @@
       </c>
       <c r="B276" s="17" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Patio Lomas Estrella</t>
+          <t>Patio Boturini</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -12605,17 +12605,17 @@
       </c>
       <c r="B277" s="16" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>Patio Revolución</t>
+          <t>Patio Lomas Estrella</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E277" s="11" t="n">
@@ -12645,17 +12645,17 @@
       </c>
       <c r="B278" s="17" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Patio Tlalpan</t>
+          <t>Patio Revolución</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
@@ -12685,17 +12685,17 @@
       </c>
       <c r="B279" s="16" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>Patio Universidad</t>
+          <t>Patio Tlalpan</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E279" s="11" t="n">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="B280" s="17" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>Pedregal</t>
+          <t>Patio Universidad</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
@@ -12765,17 +12765,17 @@
       </c>
       <c r="B281" s="16" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>PeriSur</t>
+          <t>Pedregal</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
@@ -12805,17 +12805,17 @@
       </c>
       <c r="B282" s="17" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>Periferico Polanco DT</t>
+          <t>PeriSur</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
@@ -12845,17 +12845,17 @@
       </c>
       <c r="B283" s="16" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>Perisur Reserve</t>
+          <t>Periferico Polanco DT</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
@@ -12885,17 +12885,17 @@
       </c>
       <c r="B284" s="17" t="inlineStr">
         <is>
-          <t>38482</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>Pestalozzi</t>
+          <t>Perisur Reserve</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
@@ -12925,17 +12925,17 @@
       </c>
       <c r="B285" s="16" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>Picacho Ajusco</t>
+          <t>Pestalozzi</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
@@ -12965,17 +12965,17 @@
       </c>
       <c r="B286" s="17" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>Pilares</t>
+          <t>Picacho Ajusco</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
@@ -13005,17 +13005,17 @@
       </c>
       <c r="B287" s="16" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>Plaza Alameda</t>
+          <t>Pilares</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
@@ -13045,17 +13045,17 @@
       </c>
       <c r="B288" s="17" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>Plaza America DT</t>
+          <t>Plaza Alameda</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
@@ -13085,17 +13085,17 @@
       </c>
       <c r="B289" s="16" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aragon</t>
+          <t>Plaza America DT</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
@@ -13125,17 +13125,17 @@
       </c>
       <c r="B290" s="17" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Plaza Basica</t>
+          <t>Plaza Aragon</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
@@ -13165,12 +13165,12 @@
       </c>
       <c r="B291" s="16" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>Plaza Central</t>
+          <t>Plaza Basica</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
@@ -13205,17 +13205,17 @@
       </c>
       <c r="B292" s="17" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Plaza Chimalhuacan</t>
+          <t>Plaza Central</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
@@ -13245,17 +13245,17 @@
       </c>
       <c r="B293" s="16" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>Plaza Cuicuilco</t>
+          <t>Plaza Chimalhuacan</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E293" s="11" t="n">
@@ -13285,17 +13285,17 @@
       </c>
       <c r="B294" s="17" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Alta</t>
+          <t>Plaza Cuicuilco</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
@@ -13325,12 +13325,12 @@
       </c>
       <c r="B295" s="16" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38173</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Baja</t>
+          <t>Plaza Delta Planta Alta</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
@@ -13365,17 +13365,17 @@
       </c>
       <c r="B296" s="17" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Plaza Ermita</t>
+          <t>Plaza Delta Planta Baja</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="B297" s="16" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>Plaza Inn</t>
+          <t>Plaza Ermita</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E297" s="11" t="n">
@@ -13445,17 +13445,17 @@
       </c>
       <c r="B298" s="17" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="C298" s="8" t="inlineStr">
         <is>
-          <t>Plaza Luis Cabrera</t>
+          <t>Plaza Inn</t>
         </is>
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
@@ -13485,17 +13485,17 @@
       </c>
       <c r="B299" s="16" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>Plaza Oriente l</t>
+          <t>Plaza Luis Cabrera</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E299" s="11" t="n">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="B300" s="17" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="C300" s="8" t="inlineStr">
         <is>
-          <t>Plaza Oriente ll</t>
+          <t>Plaza Oriente l</t>
         </is>
       </c>
       <c r="D300" s="8" t="inlineStr">
@@ -13565,17 +13565,17 @@
       </c>
       <c r="B301" s="16" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>Plaza Santa Teresa</t>
+          <t>Plaza Oriente ll</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E301" s="11" t="n">
@@ -13605,17 +13605,17 @@
       </c>
       <c r="B302" s="17" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="C302" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepozán</t>
+          <t>Plaza Santa Teresa</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
@@ -13645,17 +13645,17 @@
       </c>
       <c r="B303" s="16" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tlatelolco</t>
+          <t>Plaza Tepozán</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E303" s="11" t="n">
@@ -13685,17 +13685,17 @@
       </c>
       <c r="B304" s="17" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="C304" s="8" t="inlineStr">
         <is>
-          <t>Plaza Universidad</t>
+          <t>Plaza Tlatelolco</t>
         </is>
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
@@ -13725,17 +13725,17 @@
       </c>
       <c r="B305" s="16" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>Plaza Zapotitlán DT</t>
+          <t>Plaza Universidad</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E305" s="11" t="n">
@@ -13765,17 +13765,17 @@
       </c>
       <c r="B306" s="17" t="inlineStr">
         <is>
-          <t>38360</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="C306" s="8" t="inlineStr">
         <is>
-          <t>Plaza la Hacienda</t>
+          <t>Plaza Zapotitlán DT</t>
         </is>
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
@@ -13805,17 +13805,17 @@
       </c>
       <c r="B307" s="16" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>Portal Churubusco</t>
+          <t>Plaza la Hacienda</t>
         </is>
       </c>
       <c r="D307" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E307" s="11" t="n">
@@ -13845,17 +13845,17 @@
       </c>
       <c r="B308" s="17" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="C308" s="8" t="inlineStr">
         <is>
-          <t>Power Center las Americas</t>
+          <t>Portal Churubusco</t>
         </is>
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
@@ -13885,17 +13885,17 @@
       </c>
       <c r="B309" s="16" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>Prisma Insurgentes</t>
+          <t>Power Center las Americas</t>
         </is>
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E309" s="11" t="n">
@@ -13925,17 +13925,17 @@
       </c>
       <c r="B310" s="17" t="inlineStr">
         <is>
-          <t>43183</t>
+          <t>38430</t>
         </is>
       </c>
       <c r="C310" s="8" t="inlineStr">
         <is>
-          <t>Puerta Texcoco</t>
+          <t>Prisma Insurgentes</t>
         </is>
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
@@ -13965,17 +13965,17 @@
       </c>
       <c r="B311" s="16" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>43183</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>Punto MAQ</t>
+          <t>Puerta Texcoco</t>
         </is>
       </c>
       <c r="D311" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E311" s="11" t="n">
@@ -14005,17 +14005,17 @@
       </c>
       <c r="B312" s="17" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="C312" s="8" t="inlineStr">
         <is>
-          <t>Punto Polanco</t>
+          <t>Punto MAQ</t>
         </is>
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E312" s="7" t="n">
@@ -14045,17 +14045,17 @@
       </c>
       <c r="B313" s="16" t="inlineStr">
         <is>
-          <t>38654</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>Reforma 180</t>
+          <t>Punto Polanco</t>
         </is>
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E313" s="11" t="n">
@@ -14085,12 +14085,12 @@
       </c>
       <c r="B314" s="17" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>38654</t>
         </is>
       </c>
       <c r="C314" s="8" t="inlineStr">
         <is>
-          <t>Reforma 222</t>
+          <t>Reforma 180</t>
         </is>
       </c>
       <c r="D314" s="8" t="inlineStr">
@@ -14125,12 +14125,12 @@
       </c>
       <c r="B315" s="16" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>Reforma 222 II</t>
+          <t>Reforma 222</t>
         </is>
       </c>
       <c r="D315" s="12" t="inlineStr">
@@ -14165,17 +14165,17 @@
       </c>
       <c r="B316" s="17" t="inlineStr">
         <is>
-          <t>38560</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="C316" s="8" t="inlineStr">
         <is>
-          <t>Renato Leduc</t>
+          <t>Reforma 222 II</t>
         </is>
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E316" s="7" t="n">
@@ -14205,17 +14205,17 @@
       </c>
       <c r="B317" s="16" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>38560</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>Rio Hudson</t>
+          <t>Renato Leduc</t>
         </is>
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E317" s="11" t="n">
@@ -14245,17 +14245,17 @@
       </c>
       <c r="B318" s="17" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="C318" s="8" t="inlineStr">
         <is>
-          <t>Rio Marne</t>
+          <t>Rio Hudson</t>
         </is>
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
@@ -14285,17 +14285,17 @@
       </c>
       <c r="B319" s="16" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>Rio San Joaquin</t>
+          <t>Rio Marne</t>
         </is>
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E319" s="11" t="n">
@@ -14325,17 +14325,17 @@
       </c>
       <c r="B320" s="17" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="C320" s="8" t="inlineStr">
         <is>
-          <t>Rojo Gomez DT</t>
+          <t>Rio San Joaquin</t>
         </is>
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
@@ -14365,17 +14365,17 @@
       </c>
       <c r="B321" s="16" t="inlineStr">
         <is>
-          <t>38558</t>
+          <t>43070</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>Roma Sur</t>
+          <t>Rojo Gomez DT</t>
         </is>
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E321" s="11" t="n">
@@ -14405,17 +14405,17 @@
       </c>
       <c r="B322" s="17" t="inlineStr">
         <is>
-          <t>38653</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="C322" s="8" t="inlineStr">
         <is>
-          <t>Salon Ejecutivo T1 AICM</t>
+          <t>Roma Sur</t>
         </is>
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
@@ -14445,17 +14445,17 @@
       </c>
       <c r="B323" s="16" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>San Jeronimo</t>
+          <t>Salon Ejecutivo T1 AICM</t>
         </is>
       </c>
       <c r="D323" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E323" s="11" t="n">
@@ -14485,17 +14485,17 @@
       </c>
       <c r="B324" s="17" t="inlineStr">
         <is>
-          <t>38417</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="C324" s="8" t="inlineStr">
         <is>
-          <t>San Jose Insurgentes</t>
+          <t>San Jeronimo</t>
         </is>
       </c>
       <c r="D324" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E324" s="7" t="n">
@@ -14525,17 +14525,17 @@
       </c>
       <c r="B325" s="16" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38417</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>San Jose Insurgentes</t>
         </is>
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E325" s="11" t="n">
@@ -14565,17 +14565,17 @@
       </c>
       <c r="B326" s="17" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>38513</t>
         </is>
       </c>
       <c r="C326" s="8" t="inlineStr">
         <is>
-          <t>San Marcos DT</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="D326" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E326" s="7" t="n">
@@ -14605,17 +14605,17 @@
       </c>
       <c r="B327" s="16" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>Santa Teresa</t>
+          <t>San Marcos DT</t>
         </is>
       </c>
       <c r="D327" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E327" s="11" t="n">
@@ -14645,17 +14645,17 @@
       </c>
       <c r="B328" s="17" t="inlineStr">
         <is>
-          <t>38659</t>
+          <t>38116</t>
         </is>
       </c>
       <c r="C328" s="8" t="inlineStr">
         <is>
-          <t>Sendero Ixtapaluca</t>
+          <t>Santa Teresa</t>
         </is>
       </c>
       <c r="D328" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E328" s="7" t="n">
@@ -14685,17 +14685,17 @@
       </c>
       <c r="B329" s="16" t="inlineStr">
         <is>
-          <t>38764</t>
+          <t>38659</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Napoles</t>
+          <t>Sendero Ixtapaluca</t>
         </is>
       </c>
       <c r="D329" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E329" s="11" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
+          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
         </is>
       </c>
     </row>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="E16" s="9">
         <f>IFERROR(C16/(C16+D16),0)</f>
@@ -16565,7 +16565,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 10:25</t>
+          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
+          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -732,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
+          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
         </is>
       </c>
     </row>
@@ -2405,17 +2405,17 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -2445,37 +2445,37 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
         <v>9</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
         <v/>
       </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2525,17 +2525,17 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>3</v>
@@ -2685,24 +2685,24 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
         <v>8</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2965,21 +2965,21 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>4</v>
@@ -3005,17 +3005,17 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
+          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
         </is>
       </c>
     </row>
@@ -16246,10 +16246,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E16" s="9">
         <f>IFERROR(C16/(C16+D16),0)</f>
@@ -16565,7 +16565,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 17:54</t>
+          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
+          <t>Todas las regiones · Corte 17/09/2026 11:56</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -732,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
+          <t>Todas las regiones · Corte 17/09/2026 11:56</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2285,17 +2285,17 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>2</v>
@@ -2365,17 +2365,17 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2445,17 +2445,17 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
         <v/>
       </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
+          <t>Todas las regiones · Corte 17/09/2026 11:56</t>
         </is>
       </c>
     </row>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E16" s="9">
         <f>IFERROR(C16/(C16+D16),0)</f>
@@ -16565,7 +16565,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 15/09/2026 19:02</t>
+          <t>Todas las regiones · Corte 17/09/2026 11:56</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -857,17 +857,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -890,17 +890,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Andrea Nava</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(D16/(D16+E16),0)</f>
@@ -1161,10 +1161,10 @@
         <v>13</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(D24/(D24+E24),0)</f>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Fernando Verdugo</t>
+          <t>Ariana Gutierrez</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F25" s="13">
         <f>IFERROR(D25/(D25+E25),0)</f>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ariana Gutierrez</t>
+          <t>Cesar Castillo</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(D26/(D26+E26),0)</f>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Cesar Castillo</t>
+          <t>Fernando Verdugo</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F27" s="13">
         <f>IFERROR(D27/(D27+E27),0)</f>
@@ -1845,17 +1845,17 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2062,7 +2062,7 @@
         <v>7</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>3</v>
@@ -3045,17 +3045,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -3085,21 +3085,21 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>6</v>
@@ -3108,14 +3108,14 @@
         <f>IFERROR(E39/(E39+F39),0)</f>
         <v/>
       </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3125,24 +3125,24 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -3205,17 +3205,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -4445,17 +4445,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -4565,17 +4565,17 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4605,17 +4605,17 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -4805,17 +4805,17 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5205,17 +5205,17 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
@@ -6965,17 +6965,17 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -7045,17 +7045,17 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -7085,17 +7085,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7125,17 +7125,17 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -7285,17 +7285,17 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
@@ -7445,17 +7445,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
@@ -7805,17 +7805,17 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7885,17 +7885,17 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,24 +8405,24 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G172" s="9">
         <f>IFERROR(E172/(E172+F172),0)</f>
@@ -8445,24 +8445,24 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G173" s="13">
         <f>IFERROR(E173/(E173+F173),0)</f>
@@ -8485,17 +8485,17 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
@@ -8685,17 +8685,17 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E179" s="11" t="n">
@@ -8725,17 +8725,17 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
@@ -9005,17 +9005,17 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
@@ -9085,17 +9085,17 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
@@ -9205,17 +9205,17 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E192" s="7" t="n">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
@@ -9325,17 +9325,17 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9445,17 +9445,17 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9565,17 +9565,17 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9845,17 +9845,17 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9925,12 +9925,12 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>Ciudad Jardin ll</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
@@ -9965,17 +9965,17 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Ciudad Jardin ll</t>
+          <t>Coapa Chedraui</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Coapa Chedraui</t>
+          <t>Condesa</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -10045,17 +10045,17 @@
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Condesa</t>
+          <t>Copilco 20</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Copilco 20</t>
+          <t>Corporativo Coyoacan</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E214" s="7" t="n">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Coyoacan</t>
+          <t>Corporativo HSBC</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
@@ -10165,17 +10165,17 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Corporativo HSBC</t>
+          <t>Corporativo Polanco</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Polanco</t>
+          <t>Coyoacan Centro</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
@@ -10245,17 +10245,17 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>Coyoacan Centro</t>
+          <t>Division del Norte</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="B219" s="15" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>Division del Norte</t>
+          <t>Division del Norte II</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
@@ -10325,17 +10325,17 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Division del Norte II</t>
+          <t>Ejercito Nacional</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
@@ -10365,17 +10365,17 @@
       </c>
       <c r="B221" s="15" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>Ejercito Nacional</t>
+          <t>Embassy Suites</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
@@ -10405,17 +10405,17 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>Embassy Suites</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
@@ -10445,17 +10445,17 @@
       </c>
       <c r="B223" s="15" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Fiesta Americana Reforma</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
@@ -10485,17 +10485,17 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>Fiesta Americana Reforma</t>
+          <t>Forum Buenavista</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
@@ -10525,12 +10525,12 @@
       </c>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Forum Buenavista</t>
+          <t>Forum Buenavista II</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Forum Buenavista II</t>
+          <t>Galerias Coapa</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
@@ -10605,17 +10605,17 @@
       </c>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Galerias Coapa</t>
+          <t>Galerias metepec 1</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
@@ -10645,17 +10645,17 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Galerias metepec 1</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
@@ -10685,17 +10685,17 @@
       </c>
       <c r="B229" s="15" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Gran Sur</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
@@ -10725,17 +10725,17 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Gran Sur</t>
+          <t>Grand San Jeronimo</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
@@ -10765,17 +10765,17 @@
       </c>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Grand San Jeronimo</t>
+          <t>Homero</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Homero</t>
+          <t>Hospital Angeles Clinica Londres</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles Clinica Londres</t>
+          <t>Hospital Angeles Metropolitano</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
@@ -10885,17 +10885,17 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles Metropolitano</t>
+          <t>Hospital Angeles del Pedregal</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="B235" s="15" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal</t>
+          <t>Hospital Angeles del Pedregal II</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
@@ -10965,17 +10965,17 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal II</t>
+          <t>Insurgentes Relox</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="B237" s="15" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Relox</t>
+          <t>Insurgentes Tehuantepec</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
@@ -11045,17 +11045,17 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Tehuantepec</t>
+          <t>Insurgentes Wtc</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
@@ -11085,17 +11085,17 @@
       </c>
       <c r="B239" s="15" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Wtc</t>
+          <t>Interlomas</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
@@ -11125,17 +11125,17 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>38219</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Irrigacion</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
@@ -11165,17 +11165,17 @@
       </c>
       <c r="B241" s="15" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>Irrigacion</t>
+          <t>Jardines del Pedregal</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Jardines del Pedregal</t>
+          <t>Jolie Place</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
@@ -11245,17 +11245,17 @@
       </c>
       <c r="B243" s="15" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Jolie Place</t>
+          <t>Juan Pablo II</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
@@ -11285,17 +11285,17 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Juan Pablo II</t>
+          <t>Juarez 32</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
@@ -11325,17 +11325,17 @@
       </c>
       <c r="B245" s="15" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>Juarez 32</t>
+          <t>La Salle</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E245" s="11" t="n">
@@ -11365,24 +11365,24 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F246" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G246" s="9">
         <f>IFERROR(E246/(E246+F246),0)</f>
@@ -11405,24 +11405,24 @@
       </c>
       <c r="B247" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G247" s="13">
         <f>IFERROR(E247/(E247+F247),0)</f>
@@ -11445,17 +11445,17 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Macroplaza Tecamac</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
@@ -11485,17 +11485,17 @@
       </c>
       <c r="B249" s="15" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Macroplaza Tecamac</t>
+          <t>Madero</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
@@ -11525,17 +11525,17 @@
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Madero</t>
+          <t>Masarik</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B251" s="15" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>Masarik</t>
+          <t>Masarik Spencer</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Masarik Spencer</t>
+          <t>Medica Sur</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
@@ -11645,17 +11645,17 @@
       </c>
       <c r="B253" s="15" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>Medica Sur</t>
+          <t>Mexfund Pedregal</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
@@ -11685,17 +11685,17 @@
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Mexfund Pedregal</t>
+          <t>Miguel Angel de Quevedo II</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="B255" s="15" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo II</t>
+          <t>Miguel Angel de Quevedo III</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
@@ -11765,17 +11765,17 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo III</t>
+          <t>Miramontes</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
@@ -11805,17 +11805,17 @@
       </c>
       <c r="B257" s="15" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>Miramontes</t>
+          <t>Mitikah</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
@@ -11845,12 +11845,12 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>Mitikah</t>
+          <t>Mitikah Restaurantes</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
@@ -11885,17 +11885,17 @@
       </c>
       <c r="B259" s="15" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>Mitikah Restaurantes</t>
+          <t>Miyana</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E259" s="11" t="n">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Miyana</t>
+          <t>Miyana II</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="B261" s="15" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>Miyana II</t>
+          <t>Moliere 222</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E261" s="11" t="n">
@@ -12005,17 +12005,17 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Moliere 222</t>
+          <t>Montecitos Wtc</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>Montecitos Wtc</t>
+          <t>Multiplaza Bosques</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
@@ -12085,17 +12085,17 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Multiplaza Bosques</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 17/09/2026 22:29</t>
+          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3180</v>
+        <v>3171</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -798,10 +798,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -831,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado</t>
+          <t>Monica Morales</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(D24/(D24+E24),0)</f>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Ariana Gutierrez</t>
+          <t>Alberto Torrado</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F25" s="13">
         <f>IFERROR(D25/(D25+E25),0)</f>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Cesar Castillo</t>
+          <t>Ariana Gutierrez</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(D26/(D26+E26),0)</f>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Fernando Verdugo</t>
+          <t>Cesar Castillo</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F27" s="13">
         <f>IFERROR(D27/(D27+E27),0)</f>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra</t>
+          <t>Fernando Verdugo</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Hazar Trejo</t>
+          <t>Guadalupe Ibarra</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes</t>
+          <t>Hazar Trejo</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(D30/(D30+E30),0)</f>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Jesus Elguera</t>
+          <t>Jaqueline Cortes</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F31" s="13">
         <f>IFERROR(D31/(D31+E31),0)</f>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Luis Neri</t>
+          <t>Jesus Elguera</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(D32/(D32+E32),0)</f>
@@ -1451,17 +1451,17 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Luis Quevedo</t>
+          <t>Luis Neri</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F33" s="13">
         <f>IFERROR(D33/(D33+E33),0)</f>
@@ -1484,17 +1484,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Maria Sanchez</t>
+          <t>Luis Quevedo</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(D34/(D34+E34),0)</f>
@@ -1517,17 +1517,17 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Monica Morales</t>
+          <t>Maria Sanchez</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="F35" s="13">
         <f>IFERROR(D35/(D35+E35),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 17/09/2026 22:29</t>
+          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2605,21 +2605,21 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>4</v>
@@ -2645,17 +2645,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2685,24 +2685,24 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
         <v>5</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -2725,24 +2725,24 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -3005,21 +3005,21 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>5</v>
@@ -3045,17 +3045,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -3125,21 +3125,21 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>6</v>
@@ -3148,14 +3148,14 @@
         <f>IFERROR(E40/(E40+F40),0)</f>
         <v/>
       </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3165,24 +3165,24 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3285,17 +3285,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3365,24 +3365,24 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
@@ -3445,24 +3445,24 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -3485,24 +3485,24 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" s="13">
         <f>IFERROR(E49/(E49+F49),0)</f>
@@ -3525,24 +3525,24 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -3565,24 +3565,24 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -4805,17 +4805,17 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5205,17 +5205,17 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
@@ -6965,17 +6965,17 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
@@ -7085,17 +7085,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -7445,17 +7445,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7645,12 +7645,12 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
@@ -7805,17 +7805,17 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,24 +8405,24 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G172" s="9">
         <f>IFERROR(E172/(E172+F172),0)</f>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
@@ -8485,17 +8485,17 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
@@ -8685,17 +8685,17 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E179" s="11" t="n">
@@ -8725,17 +8725,17 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
@@ -9005,17 +9005,17 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
@@ -9085,17 +9085,17 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
@@ -9205,17 +9205,17 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E192" s="7" t="n">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
@@ -9325,17 +9325,17 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9445,17 +9445,17 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 17/09/2026 22:29</t>
+          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16246,10 +16246,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -16319,7 +16319,7 @@
         <v>24</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16495,7 +16495,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 17/09/2026 22:29</t>
+          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$361</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$118</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jarras'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
+          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3171</v>
+        <v>3159</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -692,17 +692,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Enrique César</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -725,17 +725,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Enrique César</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
+          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1845,37 +1845,37 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
         <v/>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1885,21 +1885,21 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>2</v>
@@ -1908,14 +1908,14 @@
         <f>IFERROR(E9/(E9+F9),0)</f>
         <v/>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1925,21 +1925,21 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>2</v>
@@ -1948,14 +1948,14 @@
         <f>IFERROR(E10/(E10+F10),0)</f>
         <v/>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1965,21 +1965,21 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>2</v>
@@ -1988,14 +1988,14 @@
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -2085,24 +2085,24 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -2125,24 +2125,24 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
         <v>7</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2182,7 +2182,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>3</v>
@@ -2285,24 +2285,24 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -2325,24 +2325,24 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -2382,7 +2382,7 @@
         <v>6</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2645,21 +2645,21 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>4</v>
@@ -2685,21 +2685,21 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>4</v>
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2765,24 +2765,24 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
         <v>5</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -2805,17 +2805,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
+          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16386,10 +16386,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16472,7 +16472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16495,7 +16495,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 18/09/2026 21:56</t>
+          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -16663,12 +16663,12 @@
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -16687,19 +16687,19 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890002429465249863001798263915_Starbucks%20Luna%20Park.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_8223_Starbucks%20Mega%20Izcal.jpeg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -16711,26 +16711,26 @@
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894098786624170437606810729851_Ramon%20Espinosa%20Macia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890002429465249863001798263915_Starbucks%20Luna%20Park.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -16739,60 +16739,60 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260915_084807860_HDR_Starbucks%20San%20Miguel.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894098786624170437606810729851_Ramon%20Espinosa%20Macia.jpg</t>
         </is>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Arboledas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260915_084807860_HDR_Starbucks%20San%20Miguel.jpg</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -16801,34 +16801,34 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Arboledas.jpg</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -16842,50 +16842,50 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -16897,26 +16897,26 @@
         <v>3</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -16925,29 +16925,29 @@
         </is>
       </c>
       <c r="D17" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="F17" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/16E0A561-50F1-438C-86F0-F70E0E2910FB_Starbucks%20El%20Rosario.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -16956,29 +16956,29 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/16E0A561-50F1-438C-86F0-F70E0E2910FB_Starbucks%20El%20Rosario.jpeg</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -16987,29 +16987,29 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -17018,29 +17018,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -17059,50 +17059,50 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
         </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -17111,29 +17111,29 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -17142,29 +17142,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -17173,29 +17173,29 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -17207,26 +17207,26 @@
         <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -17235,29 +17235,29 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -17266,29 +17266,29 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -17297,29 +17297,29 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -17338,19 +17338,19 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -17362,26 +17362,26 @@
         <v>2</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -17390,29 +17390,29 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -17431,50 +17431,50 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -17493,19 +17493,19 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -17514,29 +17514,29 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -17545,29 +17545,29 @@
         </is>
       </c>
       <c r="D37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -17579,26 +17579,26 @@
         <v>2</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -17617,19 +17617,19 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
         </is>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -17638,29 +17638,29 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -17669,60 +17669,60 @@
         </is>
       </c>
       <c r="D41" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
         </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -17741,19 +17741,19 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -17762,29 +17762,29 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -17793,29 +17793,29 @@
         </is>
       </c>
       <c r="D45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -17824,29 +17824,29 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -17855,29 +17855,29 @@
         </is>
       </c>
       <c r="D47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -17896,19 +17896,19 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -17927,19 +17927,19 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -17958,19 +17958,19 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -17989,19 +17989,19 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -18020,19 +18020,19 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -18044,57 +18044,57 @@
         <v>2</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -18103,29 +18103,29 @@
         </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -18134,29 +18134,29 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -18165,29 +18165,29 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
         </is>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -18199,26 +18199,26 @@
         <v>1</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -18227,29 +18227,29 @@
         </is>
       </c>
       <c r="D59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -18258,29 +18258,29 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -18299,19 +18299,19 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -18323,26 +18323,26 @@
         <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -18351,29 +18351,29 @@
         </is>
       </c>
       <c r="D63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -18382,34 +18382,34 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
@@ -18423,19 +18423,19 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
         </is>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -18444,29 +18444,29 @@
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -18475,29 +18475,29 @@
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -18509,26 +18509,26 @@
         <v>1</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -18537,29 +18537,29 @@
         </is>
       </c>
       <c r="D69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
         </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -18578,19 +18578,19 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -18609,19 +18609,19 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
         </is>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -18640,19 +18640,19 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -18671,19 +18671,19 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
         </is>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -18692,29 +18692,29 @@
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
         </is>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -18733,19 +18733,19 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
         </is>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -18754,29 +18754,29 @@
         </is>
       </c>
       <c r="D76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E76" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -18785,29 +18785,29 @@
         </is>
       </c>
       <c r="D77" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
         </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
       <c r="A78" s="17" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -18819,26 +18819,26 @@
         <v>1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
         </is>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -18847,60 +18847,60 @@
         </is>
       </c>
       <c r="D79" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
         </is>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
         </is>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -18919,19 +18919,19 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -18940,29 +18940,29 @@
         </is>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
         </is>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -18981,19 +18981,19 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
         </is>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -19002,29 +19002,29 @@
         </is>
       </c>
       <c r="D84" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E84" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
         </is>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -19036,26 +19036,26 @@
         <v>2</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
         </is>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -19064,29 +19064,29 @@
         </is>
       </c>
       <c r="D86" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -19095,29 +19095,29 @@
         </is>
       </c>
       <c r="D87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
         </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -19126,29 +19126,29 @@
         </is>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
         </is>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -19167,19 +19167,19 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
         </is>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -19198,19 +19198,19 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
         </is>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -19219,29 +19219,29 @@
         </is>
       </c>
       <c r="D91" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -19250,29 +19250,29 @@
         </is>
       </c>
       <c r="D92" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -19281,29 +19281,29 @@
         </is>
       </c>
       <c r="D93" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
         </is>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -19312,60 +19312,60 @@
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
         </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="D95" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E95" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F95" s="11" t="n">
-        <v>5</v>
-      </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -19377,26 +19377,26 @@
         <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -19415,19 +19415,19 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -19436,29 +19436,29 @@
         </is>
       </c>
       <c r="D98" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E98" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
         </is>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -19467,29 +19467,29 @@
         </is>
       </c>
       <c r="D99" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -19508,19 +19508,19 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
         </is>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -19532,26 +19532,26 @@
         <v>2</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -19560,29 +19560,29 @@
         </is>
       </c>
       <c r="D102" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
         </is>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -19591,29 +19591,29 @@
         </is>
       </c>
       <c r="D103" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E103" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
         </is>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
@@ -19632,50 +19632,50 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
         </is>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="D105" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E105" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F105" s="11" t="n">
-        <v>6</v>
-      </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -19684,29 +19684,29 @@
         </is>
       </c>
       <c r="D106" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
         </is>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -19718,26 +19718,26 @@
         <v>1</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
         </is>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -19746,29 +19746,29 @@
         </is>
       </c>
       <c r="D108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
         </is>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -19777,29 +19777,29 @@
         </is>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
         </is>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
@@ -19808,29 +19808,29 @@
         </is>
       </c>
       <c r="D110" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E110" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
         </is>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -19849,19 +19849,19 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
         </is>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -19870,29 +19870,29 @@
         </is>
       </c>
       <c r="D112" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
         </is>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -19901,29 +19901,29 @@
         </is>
       </c>
       <c r="D113" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
         </is>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -19932,29 +19932,29 @@
         </is>
       </c>
       <c r="D114" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
         </is>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -19966,26 +19966,26 @@
         <v>2</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
         </is>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -20004,19 +20004,19 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -20028,41 +20028,72 @@
         <v>2</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="21" customHeight="1">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>38644</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Torre Virreyes</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G117" s="12" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891464434056746458223120183687_Starbucks%20Torre%20Virr.jpg</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="21" customHeight="1">
-      <c r="A118" s="18" t="n"/>
-      <c r="B118" s="19" t="n"/>
-      <c r="C118" s="19" t="inlineStr">
+    <row r="119" ht="21" customHeight="1">
+      <c r="A119" s="18" t="n"/>
+      <c r="B119" s="19" t="n"/>
+      <c r="C119" s="19" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
       </c>
-      <c r="D118" s="20">
-        <f>SUM(D5:D117)</f>
-        <v/>
-      </c>
-      <c r="E118" s="20">
-        <f>SUM(E5:E117)</f>
-        <v/>
-      </c>
-      <c r="F118" s="20">
-        <f>SUM(F5:F117)</f>
-        <v/>
-      </c>
-      <c r="G118" s="19" t="n"/>
+      <c r="D119" s="20">
+        <f>SUM(D5:D118)</f>
+        <v/>
+      </c>
+      <c r="E119" s="20">
+        <f>SUM(E5:E118)</f>
+        <v/>
+      </c>
+      <c r="F119" s="20">
+        <f>SUM(F5:F118)</f>
+        <v/>
+      </c>
+      <c r="G119" s="19" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G117"/>
+  <autoFilter ref="A4:G118"/>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:G2"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
+          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3516</v>
+        <v>3514</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -798,10 +798,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -864,10 +864,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
+          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
         </is>
       </c>
     </row>
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3045,37 +3045,37 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
         <v/>
       </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3085,17 +3085,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -3285,17 +3285,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3525,24 +3525,24 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -3565,24 +3565,24 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -3605,24 +3605,24 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -3645,17 +3645,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
+          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 14:24</t>
+          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
+          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -831,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -857,17 +857,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Andrea Nava</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -890,17 +890,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava</t>
+          <t>Manuel Avila</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(D16/(D16+E16),0)</f>
@@ -923,17 +923,17 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Manuel Avila</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F17" s="13">
         <f>IFERROR(D17/(D17+E17),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
+          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3045,37 +3045,37 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
         <v/>
       </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -3085,17 +3085,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -3125,21 +3125,21 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>7</v>
@@ -3165,24 +3165,24 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -3605,24 +3605,24 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -3645,24 +3645,24 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
+          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16456,10 +16456,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 15:31</t>
+          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$361</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$119</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jarras'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3515</v>
+        <v>3508</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -699,10 +699,10 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -732,10 +732,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -798,10 +798,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -831,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -890,7 +890,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manuel Avila</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
@@ -900,7 +900,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(D16/(D16+E16),0)</f>
@@ -923,17 +923,17 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Manuel Avila</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F17" s="13">
         <f>IFERROR(D17/(D17+E17),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>3</v>
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -2205,24 +2205,24 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
         <v>7</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -2262,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -2285,17 +2285,17 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2365,21 +2365,21 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>4</v>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>4</v>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2462,7 +2462,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2725,21 +2725,21 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>5</v>
@@ -2765,12 +2765,12 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>5</v>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2862,7 +2862,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -3125,21 +3125,21 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>7</v>
@@ -3165,24 +3165,24 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -3245,17 +3245,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -4205,24 +4205,24 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G67" s="13">
         <f>IFERROR(E67/(E67+F67),0)</f>
@@ -4245,17 +4245,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -4285,17 +4285,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -4445,17 +4445,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -4565,17 +4565,17 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4605,17 +4605,17 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -4805,17 +4805,17 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16507,7 +16507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 16:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
         </is>
       </c>
     </row>
@@ -16760,12 +16760,12 @@
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -16777,26 +16777,26 @@
         <v>2</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894098786624170437606810729851_Ramon%20Espinosa%20Macia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17898572434496167251908049569087_Starbucks%20Patio%20Ecat.jpg</t>
         </is>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -16805,60 +16805,60 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260915_084807860_HDR_Starbucks%20San%20Miguel.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894098786624170437606810729851_Ramon%20Espinosa%20Macia.jpg</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Arboledas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260915_084807860_HDR_Starbucks%20San%20Miguel.jpg</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -16867,34 +16867,34 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Arboledas.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
@@ -16908,50 +16908,50 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -16963,26 +16963,26 @@
         <v>3</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -16991,29 +16991,29 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/16E0A561-50F1-438C-86F0-F70E0E2910FB_Starbucks%20El%20Rosario.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -17022,29 +17022,29 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/16E0A561-50F1-438C-86F0-F70E0E2910FB_Starbucks%20El%20Rosario.jpeg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -17053,29 +17053,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -17084,29 +17084,29 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
         </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -17125,50 +17125,50 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -17177,29 +17177,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -17208,29 +17208,29 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -17239,29 +17239,29 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -17273,26 +17273,26 @@
         <v>1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -17301,29 +17301,29 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -17332,29 +17332,29 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -17363,29 +17363,29 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -17404,19 +17404,19 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -17428,26 +17428,26 @@
         <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -17456,29 +17456,29 @@
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>2</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -17497,50 +17497,50 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -17559,19 +17559,19 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -17580,29 +17580,29 @@
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -17611,29 +17611,29 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -17645,26 +17645,26 @@
         <v>2</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
         </is>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -17683,19 +17683,19 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -17704,29 +17704,29 @@
         </is>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -17735,60 +17735,60 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
         </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -17807,19 +17807,19 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -17828,29 +17828,29 @@
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -17859,29 +17859,29 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -17890,29 +17890,29 @@
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -17921,29 +17921,29 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -17962,19 +17962,19 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -17993,19 +17993,19 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -18024,19 +18024,19 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -18055,19 +18055,19 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -18086,19 +18086,19 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -18110,57 +18110,57 @@
         <v>2</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D55" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -18169,29 +18169,29 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -18200,29 +18200,29 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -18231,29 +18231,29 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -18265,26 +18265,26 @@
         <v>1</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -18293,29 +18293,29 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -18324,29 +18324,29 @@
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -18365,19 +18365,19 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -18389,26 +18389,26 @@
         <v>1</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -18417,29 +18417,29 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -18448,34 +18448,34 @@
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
         </is>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="D66" s="7" t="n">
@@ -18489,19 +18489,19 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -18510,29 +18510,29 @@
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
         <v>2</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -18541,29 +18541,29 @@
         </is>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -18575,26 +18575,26 @@
         <v>1</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
         </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -18603,29 +18603,29 @@
         </is>
       </c>
       <c r="D70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -18644,19 +18644,19 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
         </is>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -18675,19 +18675,19 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -18706,19 +18706,19 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
         </is>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -18737,19 +18737,19 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
         </is>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -18758,29 +18758,29 @@
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
         </is>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -18799,19 +18799,19 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -18820,29 +18820,29 @@
         </is>
       </c>
       <c r="D77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
         </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
       <c r="A78" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -18851,29 +18851,29 @@
         </is>
       </c>
       <c r="D78" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
         </is>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -18885,26 +18885,26 @@
         <v>1</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
         </is>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -18913,60 +18913,60 @@
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
         </is>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="D81" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
         </is>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -18985,19 +18985,19 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -19006,29 +19006,29 @@
         </is>
       </c>
       <c r="D83" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
         </is>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -19047,19 +19047,19 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
         </is>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -19068,29 +19068,29 @@
         </is>
       </c>
       <c r="D85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F85" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
         </is>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -19102,26 +19102,26 @@
         <v>2</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
         </is>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -19130,29 +19130,29 @@
         </is>
       </c>
       <c r="D87" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -19161,29 +19161,29 @@
         </is>
       </c>
       <c r="D88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E88" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
         </is>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -19192,29 +19192,29 @@
         </is>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
         </is>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -19233,19 +19233,19 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
         </is>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -19264,19 +19264,19 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
         </is>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -19285,29 +19285,29 @@
         </is>
       </c>
       <c r="D92" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -19316,29 +19316,29 @@
         </is>
       </c>
       <c r="D93" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -19347,29 +19347,29 @@
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
         </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -19378,60 +19378,60 @@
         </is>
       </c>
       <c r="D95" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E95" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="D96" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F96" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -19443,26 +19443,26 @@
         <v>2</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -19481,19 +19481,19 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
         </is>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -19502,29 +19502,29 @@
         </is>
       </c>
       <c r="D99" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E99" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -19533,29 +19533,29 @@
         </is>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
         </is>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -19574,19 +19574,19 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -19598,26 +19598,26 @@
         <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
         </is>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -19626,29 +19626,29 @@
         </is>
       </c>
       <c r="D103" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
         </is>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
@@ -19657,29 +19657,29 @@
         </is>
       </c>
       <c r="D104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E104" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
         </is>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -19698,50 +19698,50 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
         </is>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="D106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E106" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>6</v>
-      </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -19750,29 +19750,29 @@
         </is>
       </c>
       <c r="D107" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
         </is>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -19784,26 +19784,26 @@
         <v>1</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
         </is>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -19812,29 +19812,29 @@
         </is>
       </c>
       <c r="D109" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
         </is>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
@@ -19843,29 +19843,29 @@
         </is>
       </c>
       <c r="D110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
         </is>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -19874,29 +19874,29 @@
         </is>
       </c>
       <c r="D111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E111" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
         </is>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -19915,19 +19915,19 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
         </is>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -19936,29 +19936,29 @@
         </is>
       </c>
       <c r="D113" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
         </is>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -19967,29 +19967,29 @@
         </is>
       </c>
       <c r="D114" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
         </is>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -19998,29 +19998,29 @@
         </is>
       </c>
       <c r="D115" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E115" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
         </is>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -20032,26 +20032,26 @@
         <v>2</v>
       </c>
       <c r="E116" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
         </is>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -20070,19 +20070,19 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
       <c r="A118" s="17" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -20094,41 +20094,72 @@
         <v>2</v>
       </c>
       <c r="E118" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="21" customHeight="1">
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>38644</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Torre Virreyes</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G118" s="8" t="inlineStr">
+      <c r="G119" s="12" t="inlineStr">
         <is>
           <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891464434056746458223120183687_Starbucks%20Torre%20Virr.jpg</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="21" customHeight="1">
-      <c r="A119" s="18" t="n"/>
-      <c r="B119" s="19" t="n"/>
-      <c r="C119" s="19" t="inlineStr">
+    <row r="120" ht="21" customHeight="1">
+      <c r="A120" s="18" t="n"/>
+      <c r="B120" s="19" t="n"/>
+      <c r="C120" s="19" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
       </c>
-      <c r="D119" s="20">
-        <f>SUM(D5:D118)</f>
-        <v/>
-      </c>
-      <c r="E119" s="20">
-        <f>SUM(E5:E118)</f>
-        <v/>
-      </c>
-      <c r="F119" s="20">
-        <f>SUM(F5:F118)</f>
-        <v/>
-      </c>
-      <c r="G119" s="19" t="n"/>
+      <c r="D120" s="20">
+        <f>SUM(D5:D119)</f>
+        <v/>
+      </c>
+      <c r="E120" s="20">
+        <f>SUM(E5:E119)</f>
+        <v/>
+      </c>
+      <c r="F120" s="20">
+        <f>SUM(F5:F119)</f>
+        <v/>
+      </c>
+      <c r="G120" s="19" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G118"/>
+  <autoFilter ref="A4:G119"/>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:G2"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -831,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -857,17 +857,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -890,17 +890,17 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Andrea Nava</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(D16/(D16+E16),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3285,17 +3285,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -3605,24 +3605,24 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -3645,24 +3645,24 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3702,7 +3702,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -3725,17 +3725,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -4165,17 +4165,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4245,24 +4245,24 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G68" s="9">
         <f>IFERROR(E68/(E68+F68),0)</f>
@@ -4285,17 +4285,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -4445,17 +4445,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -4565,17 +4565,17 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4605,17 +4605,17 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -4805,17 +4805,17 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5165,17 +5165,17 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5285,17 +5285,17 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:04</t>
+          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/21d535a4-6aa9-4964-8d4d-febb4f3b8362_Starbucks%20CC%20Coalcal.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/5342bc54-3a5b-437d-b97b-399058c7ca0c_Starbucks%20CC%20Coalcal.jpeg</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$361</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$120</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jarras'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
+          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3506</v>
+        <v>3498</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -692,17 +692,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Enrique César</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -725,17 +725,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Enrique César</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -831,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -864,10 +864,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Monica Morales</t>
+          <t>Ariana Gutierrez</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(D24/(D24+E24),0)</f>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado</t>
+          <t>Monica Morales</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F25" s="13">
         <f>IFERROR(D25/(D25+E25),0)</f>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ariana Gutierrez</t>
+          <t>Alberto Torrado</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(D26/(D26+E26),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
+          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
         </is>
       </c>
     </row>
@@ -2045,21 +2045,21 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>3</v>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2285,24 +2285,24 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
         <v>7</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2445,21 +2445,21 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>4</v>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -2502,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -2525,17 +2525,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2805,21 +2805,21 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>5</v>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>5</v>
@@ -2885,24 +2885,24 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2965,17 +2965,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3125,17 +3125,17 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -3165,21 +3165,21 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>7</v>
@@ -3205,24 +3205,24 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3645,24 +3645,24 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -3685,24 +3685,24 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3742,7 +3742,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -3765,17 +3765,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -4285,24 +4285,24 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69" s="13">
         <f>IFERROR(E69/(E69+F69),0)</f>
@@ -4325,17 +4325,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -4445,17 +4445,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -4565,17 +4565,17 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -4605,17 +4605,17 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
@@ -4685,17 +4685,17 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -4805,17 +4805,17 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5085,17 +5085,17 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5165,17 +5165,17 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -5205,17 +5205,17 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
@@ -5405,17 +5405,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
@@ -7005,17 +7005,17 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -7045,17 +7045,17 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -7125,17 +7125,17 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -7285,17 +7285,17 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -7445,17 +7445,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Oriente l</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7765,17 +7765,17 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7885,17 +7885,17 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8445,24 +8445,24 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G173" s="13">
         <f>IFERROR(E173/(E173+F173),0)</f>
@@ -8485,12 +8485,12 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
@@ -8725,17 +8725,17 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
@@ -9045,17 +9045,17 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E190" s="7" t="n">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
@@ -9285,17 +9285,17 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E194" s="7" t="n">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9445,17 +9445,17 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9565,17 +9565,17 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9845,17 +9845,17 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9925,12 +9925,12 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin ll</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
@@ -9965,17 +9965,17 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Coapa Chedraui</t>
+          <t>Ciudad Jardin ll</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Condesa</t>
+          <t>Coapa Chedraui</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -10045,17 +10045,17 @@
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Copilco 20</t>
+          <t>Condesa</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Coyoacan</t>
+          <t>Copilco 20</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E214" s="7" t="n">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>Corporativo HSBC</t>
+          <t>Corporativo Coyoacan</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
@@ -10165,17 +10165,17 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Polanco</t>
+          <t>Corporativo HSBC</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Coyoacan Centro</t>
+          <t>Corporativo Polanco</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
@@ -10245,17 +10245,17 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>Division del Norte</t>
+          <t>Coyoacan Centro</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="B219" s="15" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>Division del Norte II</t>
+          <t>Division del Norte</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
@@ -10325,17 +10325,17 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Ejercito Nacional</t>
+          <t>Division del Norte II</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
@@ -10365,17 +10365,17 @@
       </c>
       <c r="B221" s="15" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>Embassy Suites</t>
+          <t>Ejercito Nacional</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
@@ -10405,17 +10405,17 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Embassy Suites</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
@@ -10445,17 +10445,17 @@
       </c>
       <c r="B223" s="15" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Fiesta Americana Reforma</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
@@ -10485,17 +10485,17 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>Forum Buenavista</t>
+          <t>Fiesta Americana Reforma</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
@@ -10525,12 +10525,12 @@
       </c>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Forum Buenavista II</t>
+          <t>Forum Buenavista</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Galerias Coapa</t>
+          <t>Forum Buenavista II</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
@@ -10605,17 +10605,17 @@
       </c>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Galerias metepec 1</t>
+          <t>Galerias Coapa</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
@@ -10645,17 +10645,17 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Galerias metepec 1</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
@@ -10685,17 +10685,17 @@
       </c>
       <c r="B229" s="15" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Gran Sur</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
@@ -10725,17 +10725,17 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Grand San Jeronimo</t>
+          <t>Gran Sur</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
@@ -10765,17 +10765,17 @@
       </c>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Homero</t>
+          <t>Grand San Jeronimo</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles Clinica Londres</t>
+          <t>Homero</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles Metropolitano</t>
+          <t>Hospital Angeles Clinica Londres</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
@@ -10885,17 +10885,17 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal</t>
+          <t>Hospital Angeles Metropolitano</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="B235" s="15" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal II</t>
+          <t>Hospital Angeles del Pedregal</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
@@ -10965,17 +10965,17 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Relox</t>
+          <t>Hospital Angeles del Pedregal II</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="B237" s="15" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Tehuantepec</t>
+          <t>Insurgentes Relox</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
@@ -11045,17 +11045,17 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Wtc</t>
+          <t>Insurgentes Tehuantepec</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
@@ -11085,17 +11085,17 @@
       </c>
       <c r="B239" s="15" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Insurgentes Wtc</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
@@ -11125,17 +11125,17 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Irrigacion</t>
+          <t>Interlomas</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
@@ -11165,17 +11165,17 @@
       </c>
       <c r="B241" s="15" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38219</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>Jardines del Pedregal</t>
+          <t>Irrigacion</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Jolie Place</t>
+          <t>Jardines del Pedregal</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
@@ -11245,17 +11245,17 @@
       </c>
       <c r="B243" s="15" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Juan Pablo II</t>
+          <t>Jolie Place</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
@@ -11285,17 +11285,17 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Juarez 32</t>
+          <t>Juan Pablo II</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
@@ -11325,17 +11325,17 @@
       </c>
       <c r="B245" s="15" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Juarez 32</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E245" s="11" t="n">
@@ -11365,24 +11365,24 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>La Salle</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F246" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G246" s="9">
         <f>IFERROR(E246/(E246+F246),0)</f>
@@ -11405,24 +11405,24 @@
       </c>
       <c r="B247" s="15" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G247" s="13">
         <f>IFERROR(E247/(E247+F247),0)</f>
@@ -11445,17 +11445,17 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>Macroplaza Tecamac</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
@@ -11485,17 +11485,17 @@
       </c>
       <c r="B249" s="15" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Madero</t>
+          <t>Macroplaza Tecamac</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
@@ -11525,17 +11525,17 @@
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Masarik</t>
+          <t>Madero</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B251" s="15" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>Masarik Spencer</t>
+          <t>Masarik</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Medica Sur</t>
+          <t>Masarik Spencer</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
@@ -11645,17 +11645,17 @@
       </c>
       <c r="B253" s="15" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>Mexfund Pedregal</t>
+          <t>Medica Sur</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
@@ -11685,17 +11685,17 @@
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo II</t>
+          <t>Mexfund Pedregal</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="B255" s="15" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo III</t>
+          <t>Miguel Angel de Quevedo II</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
@@ -11765,17 +11765,17 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Miramontes</t>
+          <t>Miguel Angel de Quevedo III</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
@@ -11805,17 +11805,17 @@
       </c>
       <c r="B257" s="15" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>Mitikah</t>
+          <t>Miramontes</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
@@ -11845,12 +11845,12 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>Mitikah Restaurantes</t>
+          <t>Mitikah</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
@@ -11885,17 +11885,17 @@
       </c>
       <c r="B259" s="15" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>Miyana</t>
+          <t>Mitikah Restaurantes</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E259" s="11" t="n">
@@ -11925,12 +11925,12 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Miyana II</t>
+          <t>Miyana</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="B261" s="15" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>Moliere 222</t>
+          <t>Miyana II</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E261" s="11" t="n">
@@ -12005,17 +12005,17 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Montecitos Wtc</t>
+          <t>Moliere 222</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>Multiplaza Bosques</t>
+          <t>Montecitos Wtc</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
@@ -12085,17 +12085,17 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Multiplaza Bosques</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
@@ -12125,17 +12125,17 @@
       </c>
       <c r="B265" s="15" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>Oasis I</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
@@ -12165,12 +12165,12 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>Oasis II</t>
+          <t>Oasis I</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
@@ -12205,17 +12205,17 @@
       </c>
       <c r="B267" s="15" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>Obelisco</t>
+          <t>Oasis II</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E267" s="11" t="n">
@@ -12245,17 +12245,17 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>Obrero Mundial</t>
+          <t>Obelisco</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
@@ -12285,17 +12285,17 @@
       </c>
       <c r="B269" s="15" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Cuemanco</t>
+          <t>Obrero Mundial</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
@@ -12325,24 +12325,24 @@
       </c>
       <c r="B270" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Pabellon Cuemanco</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F270" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G270" s="9">
         <f>IFERROR(E270/(E270+F270),0)</f>
@@ -12365,24 +12365,24 @@
       </c>
       <c r="B271" s="15" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>Parques BBVA</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G271" s="13">
         <f>IFERROR(E271/(E271+F271),0)</f>
@@ -12405,17 +12405,17 @@
       </c>
       <c r="B272" s="17" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Parques Polanco</t>
+          <t>Parques BBVA</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
@@ -12445,17 +12445,17 @@
       </c>
       <c r="B273" s="15" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>Pasaje San Jeronimo</t>
+          <t>Parques Polanco</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E273" s="11" t="n">
@@ -12485,17 +12485,17 @@
       </c>
       <c r="B274" s="17" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Paseo Ventura</t>
+          <t>Pasaje San Jeronimo</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
@@ -12525,17 +12525,17 @@
       </c>
       <c r="B275" s="15" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>Patio Boturini</t>
+          <t>Paseo Ventura</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
@@ -12565,17 +12565,17 @@
       </c>
       <c r="B276" s="17" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Patio Lomas Estrella</t>
+          <t>Patio Boturini</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -12605,17 +12605,17 @@
       </c>
       <c r="B277" s="15" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>Patio Revolución</t>
+          <t>Patio Lomas Estrella</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E277" s="11" t="n">
@@ -12645,17 +12645,17 @@
       </c>
       <c r="B278" s="17" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Patio Tlalpan</t>
+          <t>Patio Revolución</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
@@ -12685,17 +12685,17 @@
       </c>
       <c r="B279" s="15" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>Patio Universidad</t>
+          <t>Patio Tlalpan</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E279" s="11" t="n">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="B280" s="17" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>Pedregal</t>
+          <t>Patio Universidad</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
@@ -12765,17 +12765,17 @@
       </c>
       <c r="B281" s="15" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>PeriSur</t>
+          <t>Pedregal</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
@@ -12805,17 +12805,17 @@
       </c>
       <c r="B282" s="17" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>Periferico Polanco DT</t>
+          <t>PeriSur</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
@@ -12845,17 +12845,17 @@
       </c>
       <c r="B283" s="15" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>Perisur Reserve</t>
+          <t>Periferico Polanco DT</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
@@ -12885,17 +12885,17 @@
       </c>
       <c r="B284" s="17" t="inlineStr">
         <is>
-          <t>38482</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>Pestalozzi</t>
+          <t>Perisur Reserve</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
@@ -12925,17 +12925,17 @@
       </c>
       <c r="B285" s="15" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>Picacho Ajusco</t>
+          <t>Pestalozzi</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
@@ -12965,17 +12965,17 @@
       </c>
       <c r="B286" s="17" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>Pilares</t>
+          <t>Picacho Ajusco</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
@@ -13005,17 +13005,17 @@
       </c>
       <c r="B287" s="15" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>Plaza Alameda</t>
+          <t>Pilares</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
@@ -13045,17 +13045,17 @@
       </c>
       <c r="B288" s="17" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>Plaza America DT</t>
+          <t>Plaza Alameda</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
@@ -13085,17 +13085,17 @@
       </c>
       <c r="B289" s="15" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aragon</t>
+          <t>Plaza America DT</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
@@ -13125,17 +13125,17 @@
       </c>
       <c r="B290" s="17" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Plaza Basica</t>
+          <t>Plaza Aragon</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
@@ -13165,12 +13165,12 @@
       </c>
       <c r="B291" s="15" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>Plaza Central</t>
+          <t>Plaza Basica</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
@@ -13205,17 +13205,17 @@
       </c>
       <c r="B292" s="17" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Plaza Chimalhuacan</t>
+          <t>Plaza Central</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
@@ -13245,17 +13245,17 @@
       </c>
       <c r="B293" s="15" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>Plaza Cuicuilco</t>
+          <t>Plaza Chimalhuacan</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E293" s="11" t="n">
@@ -13285,17 +13285,17 @@
       </c>
       <c r="B294" s="17" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Alta</t>
+          <t>Plaza Cuicuilco</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
@@ -13325,12 +13325,12 @@
       </c>
       <c r="B295" s="15" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38173</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Baja</t>
+          <t>Plaza Delta Planta Alta</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
@@ -13365,17 +13365,17 @@
       </c>
       <c r="B296" s="17" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Plaza Ermita</t>
+          <t>Plaza Delta Planta Baja</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="B297" s="15" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>Plaza Inn</t>
+          <t>Plaza Ermita</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E297" s="11" t="n">
@@ -13445,17 +13445,17 @@
       </c>
       <c r="B298" s="17" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="C298" s="8" t="inlineStr">
         <is>
-          <t>Plaza Luis Cabrera</t>
+          <t>Plaza Inn</t>
         </is>
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
@@ -13485,17 +13485,17 @@
       </c>
       <c r="B299" s="15" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>Plaza Oriente l</t>
+          <t>Plaza Luis Cabrera</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E299" s="11" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
+          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16281,10 +16281,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16386,10 +16386,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16507,7 +16507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 18:46</t>
+          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
         </is>
       </c>
     </row>
@@ -16822,12 +16822,12 @@
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -16836,60 +16836,60 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260915_084807860_HDR_Starbucks%20San%20Miguel.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17898694453017719363453178036313_Starbucks%20San%20Marcos.jpg</t>
         </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Arboledas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260915_084807860_HDR_Starbucks%20San%20Miguel.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -16898,34 +16898,34 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Arboledas.jpg</t>
         </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -16939,50 +16939,50 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/ChatGPT%20Image%209%20sept%202026,%2017_05_47_Enrique%20Cesar%20Flores.png</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -16994,26 +16994,26 @@
         <v>3</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1d4f59e7-23b4-41cc-97f4-4bff4f454fb1_Starbucks%20CEMTRAM%204.jpeg</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -17022,29 +17022,29 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/16E0A561-50F1-438C-86F0-F70E0E2910FB_Starbucks%20El%20Rosario.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -17053,29 +17053,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/16E0A561-50F1-438C-86F0-F70E0E2910FB_Starbucks%20El%20Rosario.jpeg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -17084,29 +17084,29 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
         </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -17115,29 +17115,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -17156,50 +17156,50 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -17208,29 +17208,29 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -17239,29 +17239,29 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -17270,29 +17270,29 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -17304,26 +17304,26 @@
         <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -17332,29 +17332,29 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -17363,29 +17363,29 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -17394,29 +17394,29 @@
         </is>
       </c>
       <c r="D31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -17435,19 +17435,19 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -17459,26 +17459,26 @@
         <v>2</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -17487,29 +17487,29 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -17528,50 +17528,50 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -17590,19 +17590,19 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -17611,29 +17611,29 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -17642,29 +17642,29 @@
         </is>
       </c>
       <c r="D39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
         </is>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -17676,26 +17676,26 @@
         <v>2</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -17714,19 +17714,19 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -17735,29 +17735,29 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
         </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -17766,60 +17766,60 @@
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -17838,19 +17838,19 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -17859,29 +17859,29 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -17890,29 +17890,29 @@
         </is>
       </c>
       <c r="D47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -17921,29 +17921,29 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -17952,29 +17952,29 @@
         </is>
       </c>
       <c r="D49" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -17993,19 +17993,19 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -18024,19 +18024,19 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -18055,19 +18055,19 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -18086,19 +18086,19 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -18117,19 +18117,19 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -18141,57 +18141,57 @@
         <v>2</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -18200,29 +18200,29 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
         </is>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -18231,29 +18231,29 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -18262,29 +18262,29 @@
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -18296,26 +18296,26 @@
         <v>1</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -18324,29 +18324,29 @@
         </is>
       </c>
       <c r="D61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -18355,29 +18355,29 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -18396,19 +18396,19 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -18420,26 +18420,26 @@
         <v>1</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -18448,29 +18448,29 @@
         </is>
       </c>
       <c r="D65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E65" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
         </is>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -18479,34 +18479,34 @@
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
@@ -18520,19 +18520,19 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -18541,29 +18541,29 @@
         </is>
       </c>
       <c r="D68" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -18572,29 +18572,29 @@
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
         </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -18606,26 +18606,26 @@
         <v>1</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -18634,29 +18634,29 @@
         </is>
       </c>
       <c r="D71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E71" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
         </is>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -18675,19 +18675,19 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -18706,19 +18706,19 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
         </is>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -18737,19 +18737,19 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
         </is>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -18768,19 +18768,19 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
         </is>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -18789,29 +18789,29 @@
         </is>
       </c>
       <c r="D76" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -18830,19 +18830,19 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
         </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
       <c r="A78" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -18851,29 +18851,29 @@
         </is>
       </c>
       <c r="D78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
         </is>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -18882,29 +18882,29 @@
         </is>
       </c>
       <c r="D79" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
         </is>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -18916,26 +18916,26 @@
         <v>1</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
         </is>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -18944,60 +18944,60 @@
         </is>
       </c>
       <c r="D81" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
         </is>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="D82" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
         </is>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -19016,19 +19016,19 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -19037,29 +19037,29 @@
         </is>
       </c>
       <c r="D84" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
         </is>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -19078,19 +19078,19 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
         </is>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -19099,29 +19099,29 @@
         </is>
       </c>
       <c r="D86" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F86" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
         </is>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -19133,26 +19133,26 @@
         <v>2</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
         </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -19161,29 +19161,29 @@
         </is>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -19192,29 +19192,29 @@
         </is>
       </c>
       <c r="D89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E89" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
         </is>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -19223,29 +19223,29 @@
         </is>
       </c>
       <c r="D90" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
         </is>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -19264,19 +19264,19 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
         </is>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -19295,19 +19295,19 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
         </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -19316,29 +19316,29 @@
         </is>
       </c>
       <c r="D93" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -19347,29 +19347,29 @@
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -19378,29 +19378,29 @@
         </is>
       </c>
       <c r="D95" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -19409,60 +19409,60 @@
         </is>
       </c>
       <c r="D96" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="D97" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F97" s="11" t="n">
-        <v>5</v>
-      </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -19474,26 +19474,26 @@
         <v>2</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
         </is>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -19512,19 +19512,19 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -19533,29 +19533,29 @@
         </is>
       </c>
       <c r="D100" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
         </is>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -19564,29 +19564,29 @@
         </is>
       </c>
       <c r="D101" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E101" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -19605,19 +19605,19 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
         </is>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -19629,26 +19629,26 @@
         <v>2</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
         </is>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
@@ -19657,29 +19657,29 @@
         </is>
       </c>
       <c r="D104" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
         </is>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -19688,29 +19688,29 @@
         </is>
       </c>
       <c r="D105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
         </is>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -19729,50 +19729,50 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
         </is>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="D107" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E107" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F107" s="11" t="n">
-        <v>6</v>
-      </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -19781,29 +19781,29 @@
         </is>
       </c>
       <c r="D108" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
         </is>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -19815,26 +19815,26 @@
         <v>1</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
         </is>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
@@ -19843,29 +19843,29 @@
         </is>
       </c>
       <c r="D110" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
         </is>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -19874,29 +19874,29 @@
         </is>
       </c>
       <c r="D111" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
         </is>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -19905,29 +19905,29 @@
         </is>
       </c>
       <c r="D112" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E112" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
         </is>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -19946,19 +19946,19 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
         </is>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -19967,29 +19967,29 @@
         </is>
       </c>
       <c r="D114" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
         </is>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -19998,29 +19998,29 @@
         </is>
       </c>
       <c r="D115" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
         </is>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -20029,29 +20029,29 @@
         </is>
       </c>
       <c r="D116" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
         </is>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -20063,26 +20063,26 @@
         <v>2</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
         </is>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
       <c r="A118" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -20101,19 +20101,19 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="119" ht="21" customHeight="1">
       <c r="A119" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -20125,41 +20125,72 @@
         <v>2</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="21" customHeight="1">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>38644</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Torre Virreyes</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G119" s="12" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891464434056746458223120183687_Starbucks%20Torre%20Virr.jpg</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="21" customHeight="1">
-      <c r="A120" s="18" t="n"/>
-      <c r="B120" s="19" t="n"/>
-      <c r="C120" s="19" t="inlineStr">
+    <row r="121" ht="21" customHeight="1">
+      <c r="A121" s="18" t="n"/>
+      <c r="B121" s="19" t="n"/>
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
       </c>
-      <c r="D120" s="20">
-        <f>SUM(D5:D119)</f>
-        <v/>
-      </c>
-      <c r="E120" s="20">
-        <f>SUM(E5:E119)</f>
-        <v/>
-      </c>
-      <c r="F120" s="20">
-        <f>SUM(F5:F119)</f>
-        <v/>
-      </c>
-      <c r="G120" s="19" t="n"/>
+      <c r="D121" s="20">
+        <f>SUM(D5:D120)</f>
+        <v/>
+      </c>
+      <c r="E121" s="20">
+        <f>SUM(E5:E120)</f>
+        <v/>
+      </c>
+      <c r="F121" s="20">
+        <f>SUM(F5:F120)</f>
+        <v/>
+      </c>
+      <c r="G121" s="19" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G119"/>
+  <autoFilter ref="A4:G120"/>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:G2"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
+          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -692,17 +692,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Enrique César</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -725,17 +725,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Enrique César</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>63</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>64</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
+          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
         </is>
       </c>
     </row>
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>2</v>
@@ -1885,37 +1885,37 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
         <v/>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1942,20 +1942,20 @@
         <v>8</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
         <v/>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -2085,21 +2085,21 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>3</v>
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
+          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 19/09/2026 22:06</t>
+          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
+          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -692,17 +692,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Enrique César</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -725,17 +725,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Enrique César</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
+          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
         </is>
       </c>
     </row>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2485,21 +2485,21 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>4</v>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2542,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
+          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 13:46</t>
+          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
+          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3495</v>
+        <v>3487</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -699,10 +699,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -732,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -798,10 +798,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -831,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
+          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1885,21 +1885,21 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>2</v>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1965,37 +1965,37 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
         <v>8</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2005,37 +2005,37 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>3</v>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2525,21 +2525,21 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>4</v>
@@ -2565,24 +2565,24 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -2605,24 +2605,24 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
         <v>6</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -2645,12 +2645,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -3245,24 +3245,24 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -3685,24 +3685,24 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="E55" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="11" t="n">
         <v>8</v>
@@ -3765,24 +3765,24 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -3805,24 +3805,24 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -3845,24 +3845,24 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -3885,17 +3885,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
+          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 14:54</t>
+          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
+          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3487</v>
+        <v>3484</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -699,10 +699,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Ariana Gutierrez</t>
+          <t>Monica Morales</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(D24/(D24+E24),0)</f>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Monica Morales</t>
+          <t>Ariana Gutierrez</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F25" s="13">
         <f>IFERROR(D25/(D25+E25),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
+          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>3</v>
@@ -2205,17 +2205,17 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2285,17 +2285,17 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -2325,24 +2325,24 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
         <v>7</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -2365,17 +2365,17 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -2445,17 +2445,17 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2525,17 +2525,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2605,21 +2605,21 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>4</v>
@@ -2645,24 +2645,24 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Ciudad Jardin ll</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
@@ -6045,17 +6045,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -6485,17 +6485,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -7045,17 +7045,17 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -7085,17 +7085,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -7285,17 +7285,17 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
@@ -7405,17 +7405,17 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -7445,17 +7445,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Plaza Oriente l</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Oriente l</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
@@ -7805,17 +7805,17 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8445,17 +8445,17 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
@@ -8485,24 +8485,24 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G174" s="9">
         <f>IFERROR(E174/(E174+F174),0)</f>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
@@ -8565,17 +8565,17 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9005,17 +9005,17 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
@@ -9085,17 +9085,17 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
@@ -9165,17 +9165,17 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
@@ -9285,17 +9285,17 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E194" s="7" t="n">
@@ -9325,17 +9325,17 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9445,17 +9445,17 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9565,17 +9565,17 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9845,17 +9845,17 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Ciudad Jardin ll</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
+          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16281,10 +16281,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 17:34</t>
+          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
+          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3484</v>
+        <v>3481</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -699,10 +699,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Monica Morales</t>
+          <t>Ariana Gutierrez</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(D24/(D24+E24),0)</f>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Ariana Gutierrez</t>
+          <t>Monica Morales</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F25" s="13">
         <f>IFERROR(D25/(D25+E25),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
+          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
         </is>
       </c>
     </row>
@@ -1725,24 +1725,24 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1805,17 +1805,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
@@ -1925,21 +1925,21 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>2</v>
@@ -1965,17 +1965,17 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2062,20 +2062,20 @@
         <v>8</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -7765,17 +7765,17 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>43070</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Rojo Gomez DT</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8445,17 +8445,17 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
@@ -8485,17 +8485,17 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8525,24 +8525,24 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G175" s="13">
         <f>IFERROR(E175/(E175+F175),0)</f>
@@ -8565,12 +8565,12 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
@@ -8605,17 +8605,17 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E177" s="11" t="n">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9005,17 +9005,17 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9045,17 +9045,17 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E190" s="7" t="n">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
@@ -9205,17 +9205,17 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E192" s="7" t="n">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
@@ -9325,17 +9325,17 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
@@ -9445,17 +9445,17 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9565,17 +9565,17 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9845,17 +9845,17 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
@@ -9965,17 +9965,17 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Coapa Chedraui</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -10045,17 +10045,17 @@
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Condesa</t>
+          <t>Coapa Chedraui</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Copilco 20</t>
+          <t>Condesa</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E214" s="7" t="n">
@@ -10125,17 +10125,17 @@
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Coyoacan</t>
+          <t>Copilco 20</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
@@ -10165,17 +10165,17 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Corporativo HSBC</t>
+          <t>Corporativo Coyoacan</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Polanco</t>
+          <t>Corporativo HSBC</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
@@ -10245,17 +10245,17 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>Coyoacan Centro</t>
+          <t>Corporativo Polanco</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
@@ -10285,17 +10285,17 @@
       </c>
       <c r="B219" s="15" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>Division del Norte</t>
+          <t>Coyoacan Centro</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E219" s="11" t="n">
@@ -10325,12 +10325,12 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Division del Norte II</t>
+          <t>Division del Norte</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
@@ -10365,17 +10365,17 @@
       </c>
       <c r="B221" s="15" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>Ejercito Nacional</t>
+          <t>Division del Norte II</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
@@ -10405,17 +10405,17 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>Embassy Suites</t>
+          <t>Ejercito Nacional</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
@@ -10445,17 +10445,17 @@
       </c>
       <c r="B223" s="15" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Embassy Suites</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
@@ -10485,17 +10485,17 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>Fiesta Americana Reforma</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
@@ -10525,17 +10525,17 @@
       </c>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Forum Buenavista</t>
+          <t>Fiesta Americana Reforma</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E225" s="11" t="n">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Forum Buenavista II</t>
+          <t>Forum Buenavista</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
@@ -10605,17 +10605,17 @@
       </c>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Galerias Coapa</t>
+          <t>Forum Buenavista II</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
@@ -10645,17 +10645,17 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Galerias metepec 1</t>
+          <t>Galerias Coapa</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
@@ -10685,17 +10685,17 @@
       </c>
       <c r="B229" s="15" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Galerias metepec 1</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
@@ -10725,17 +10725,17 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Gran Sur</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
@@ -10765,17 +10765,17 @@
       </c>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Grand San Jeronimo</t>
+          <t>Gran Sur</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Homero</t>
+          <t>Grand San Jeronimo</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
@@ -10845,17 +10845,17 @@
       </c>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles Clinica Londres</t>
+          <t>Homero</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E233" s="11" t="n">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles Metropolitano</t>
+          <t>Hospital Angeles Clinica Londres</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
@@ -10925,17 +10925,17 @@
       </c>
       <c r="B235" s="15" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal</t>
+          <t>Hospital Angeles Metropolitano</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E235" s="11" t="n">
@@ -10965,12 +10965,12 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal II</t>
+          <t>Hospital Angeles del Pedregal</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="B237" s="15" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Relox</t>
+          <t>Hospital Angeles del Pedregal II</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
@@ -11045,17 +11045,17 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Tehuantepec</t>
+          <t>Insurgentes Relox</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
@@ -11085,17 +11085,17 @@
       </c>
       <c r="B239" s="15" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Wtc</t>
+          <t>Insurgentes Tehuantepec</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
@@ -11125,17 +11125,17 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Insurgentes Wtc</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
@@ -11165,17 +11165,17 @@
       </c>
       <c r="B241" s="15" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>Irrigacion</t>
+          <t>Interlomas</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
@@ -11205,17 +11205,17 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38219</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Jardines del Pedregal</t>
+          <t>Irrigacion</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E242" s="7" t="n">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="B243" s="15" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Jolie Place</t>
+          <t>Jardines del Pedregal</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
@@ -11285,17 +11285,17 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Juan Pablo II</t>
+          <t>Jolie Place</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
@@ -11325,17 +11325,17 @@
       </c>
       <c r="B245" s="15" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>Juarez 32</t>
+          <t>Juan Pablo II</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E245" s="11" t="n">
@@ -11365,17 +11365,17 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Juarez 32</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
@@ -11405,24 +11405,24 @@
       </c>
       <c r="B247" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>La Salle</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G247" s="13">
         <f>IFERROR(E247/(E247+F247),0)</f>
@@ -11445,24 +11445,24 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F248" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G248" s="9">
         <f>IFERROR(E248/(E248+F248),0)</f>
@@ -11485,17 +11485,17 @@
       </c>
       <c r="B249" s="15" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Macroplaza Tecamac</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
@@ -11525,17 +11525,17 @@
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Madero</t>
+          <t>Macroplaza Tecamac</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B251" s="15" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>Masarik</t>
+          <t>Madero</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Masarik Spencer</t>
+          <t>Masarik</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
@@ -11645,17 +11645,17 @@
       </c>
       <c r="B253" s="15" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>Medica Sur</t>
+          <t>Masarik Spencer</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
@@ -11685,17 +11685,17 @@
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Mexfund Pedregal</t>
+          <t>Medica Sur</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
@@ -11725,17 +11725,17 @@
       </c>
       <c r="B255" s="15" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo II</t>
+          <t>Mexfund Pedregal</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E255" s="11" t="n">
@@ -11765,12 +11765,12 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo III</t>
+          <t>Miguel Angel de Quevedo II</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
@@ -11805,17 +11805,17 @@
       </c>
       <c r="B257" s="15" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>Miramontes</t>
+          <t>Miguel Angel de Quevedo III</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
@@ -11845,17 +11845,17 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>Mitikah</t>
+          <t>Miramontes</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="B259" s="15" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>Mitikah Restaurantes</t>
+          <t>Mitikah</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
@@ -11925,17 +11925,17 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Miyana</t>
+          <t>Mitikah Restaurantes</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="B261" s="15" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>Miyana II</t>
+          <t>Miyana</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
@@ -12005,17 +12005,17 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Moliere 222</t>
+          <t>Miyana II</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>Montecitos Wtc</t>
+          <t>Moliere 222</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
@@ -12085,17 +12085,17 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Multiplaza Bosques</t>
+          <t>Montecitos Wtc</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
@@ -12125,17 +12125,17 @@
       </c>
       <c r="B265" s="15" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Multiplaza Bosques</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
@@ -12165,17 +12165,17 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>Oasis I</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="B267" s="15" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>Oasis II</t>
+          <t>Oasis I</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
@@ -12245,17 +12245,17 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>Obelisco</t>
+          <t>Oasis II</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
@@ -12285,17 +12285,17 @@
       </c>
       <c r="B269" s="15" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>Obrero Mundial</t>
+          <t>Obelisco</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
@@ -12325,17 +12325,17 @@
       </c>
       <c r="B270" s="17" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Cuemanco</t>
+          <t>Obrero Mundial</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
@@ -12365,24 +12365,24 @@
       </c>
       <c r="B271" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Pabellon Cuemanco</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G271" s="13">
         <f>IFERROR(E271/(E271+F271),0)</f>
@@ -12405,24 +12405,24 @@
       </c>
       <c r="B272" s="17" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Parques BBVA</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F272" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G272" s="9">
         <f>IFERROR(E272/(E272+F272),0)</f>
@@ -12445,17 +12445,17 @@
       </c>
       <c r="B273" s="15" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>Parques Polanco</t>
+          <t>Parques BBVA</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E273" s="11" t="n">
@@ -12485,17 +12485,17 @@
       </c>
       <c r="B274" s="17" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Pasaje San Jeronimo</t>
+          <t>Parques Polanco</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
@@ -12525,17 +12525,17 @@
       </c>
       <c r="B275" s="15" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>Paseo Ventura</t>
+          <t>Pasaje San Jeronimo</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
@@ -12565,17 +12565,17 @@
       </c>
       <c r="B276" s="17" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Patio Boturini</t>
+          <t>Paseo Ventura</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -12605,17 +12605,17 @@
       </c>
       <c r="B277" s="15" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>Patio Lomas Estrella</t>
+          <t>Patio Boturini</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E277" s="11" t="n">
@@ -12645,17 +12645,17 @@
       </c>
       <c r="B278" s="17" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Patio Revolución</t>
+          <t>Patio Lomas Estrella</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
@@ -12685,17 +12685,17 @@
       </c>
       <c r="B279" s="15" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>Patio Tlalpan</t>
+          <t>Patio Revolución</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E279" s="11" t="n">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="B280" s="17" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>Patio Universidad</t>
+          <t>Patio Tlalpan</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
@@ -12765,17 +12765,17 @@
       </c>
       <c r="B281" s="15" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>Pedregal</t>
+          <t>Patio Universidad</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
@@ -12805,17 +12805,17 @@
       </c>
       <c r="B282" s="17" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>PeriSur</t>
+          <t>Pedregal</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
@@ -12845,17 +12845,17 @@
       </c>
       <c r="B283" s="15" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>Periferico Polanco DT</t>
+          <t>PeriSur</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
@@ -12885,17 +12885,17 @@
       </c>
       <c r="B284" s="17" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>Perisur Reserve</t>
+          <t>Periferico Polanco DT</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
@@ -12925,17 +12925,17 @@
       </c>
       <c r="B285" s="15" t="inlineStr">
         <is>
-          <t>38482</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>Pestalozzi</t>
+          <t>Perisur Reserve</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
@@ -12965,17 +12965,17 @@
       </c>
       <c r="B286" s="17" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>Picacho Ajusco</t>
+          <t>Pestalozzi</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
@@ -13005,17 +13005,17 @@
       </c>
       <c r="B287" s="15" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>Pilares</t>
+          <t>Picacho Ajusco</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
@@ -13045,17 +13045,17 @@
       </c>
       <c r="B288" s="17" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>Plaza Alameda</t>
+          <t>Pilares</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
@@ -13085,17 +13085,17 @@
       </c>
       <c r="B289" s="15" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>Plaza America DT</t>
+          <t>Plaza Alameda</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
@@ -13125,17 +13125,17 @@
       </c>
       <c r="B290" s="17" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aragon</t>
+          <t>Plaza America DT</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
@@ -13165,17 +13165,17 @@
       </c>
       <c r="B291" s="15" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>Plaza Basica</t>
+          <t>Plaza Aragon</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E291" s="11" t="n">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="B292" s="17" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Plaza Central</t>
+          <t>Plaza Basica</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
@@ -13245,17 +13245,17 @@
       </c>
       <c r="B293" s="15" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>Plaza Chimalhuacan</t>
+          <t>Plaza Central</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E293" s="11" t="n">
@@ -13285,17 +13285,17 @@
       </c>
       <c r="B294" s="17" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Plaza Cuicuilco</t>
+          <t>Plaza Chimalhuacan</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
@@ -13325,17 +13325,17 @@
       </c>
       <c r="B295" s="15" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Alta</t>
+          <t>Plaza Cuicuilco</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E295" s="11" t="n">
@@ -13365,12 +13365,12 @@
       </c>
       <c r="B296" s="17" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>38173</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Baja</t>
+          <t>Plaza Delta Planta Alta</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="B297" s="15" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>Plaza Ermita</t>
+          <t>Plaza Delta Planta Baja</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E297" s="11" t="n">
@@ -13445,17 +13445,17 @@
       </c>
       <c r="B298" s="17" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="C298" s="8" t="inlineStr">
         <is>
-          <t>Plaza Inn</t>
+          <t>Plaza Ermita</t>
         </is>
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
@@ -13485,17 +13485,17 @@
       </c>
       <c r="B299" s="15" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>Plaza Luis Cabrera</t>
+          <t>Plaza Inn</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E299" s="11" t="n">
@@ -13525,17 +13525,17 @@
       </c>
       <c r="B300" s="17" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="C300" s="8" t="inlineStr">
         <is>
-          <t>Plaza Oriente ll</t>
+          <t>Plaza Luis Cabrera</t>
         </is>
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E300" s="7" t="n">
@@ -13565,17 +13565,17 @@
       </c>
       <c r="B301" s="15" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>Plaza Santa Teresa</t>
+          <t>Plaza Oriente ll</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E301" s="11" t="n">
@@ -13605,17 +13605,17 @@
       </c>
       <c r="B302" s="17" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="C302" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepozán</t>
+          <t>Plaza Santa Teresa</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
@@ -13645,17 +13645,17 @@
       </c>
       <c r="B303" s="15" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tlatelolco</t>
+          <t>Plaza Tepozán</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E303" s="11" t="n">
@@ -13685,17 +13685,17 @@
       </c>
       <c r="B304" s="17" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="C304" s="8" t="inlineStr">
         <is>
-          <t>Plaza Universidad</t>
+          <t>Plaza Tlatelolco</t>
         </is>
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
@@ -13725,17 +13725,17 @@
       </c>
       <c r="B305" s="15" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>Plaza Zapotitlán DT</t>
+          <t>Plaza Universidad</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E305" s="11" t="n">
@@ -13765,17 +13765,17 @@
       </c>
       <c r="B306" s="17" t="inlineStr">
         <is>
-          <t>38360</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="C306" s="8" t="inlineStr">
         <is>
-          <t>Plaza la Hacienda</t>
+          <t>Plaza Zapotitlán DT</t>
         </is>
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
@@ -13805,17 +13805,17 @@
       </c>
       <c r="B307" s="15" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>Portal Churubusco</t>
+          <t>Plaza la Hacienda</t>
         </is>
       </c>
       <c r="D307" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E307" s="11" t="n">
@@ -13845,17 +13845,17 @@
       </c>
       <c r="B308" s="17" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="C308" s="8" t="inlineStr">
         <is>
-          <t>Power Center las Americas</t>
+          <t>Portal Churubusco</t>
         </is>
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
@@ -13885,17 +13885,17 @@
       </c>
       <c r="B309" s="15" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>Prisma Insurgentes</t>
+          <t>Power Center las Americas</t>
         </is>
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E309" s="11" t="n">
@@ -13925,17 +13925,17 @@
       </c>
       <c r="B310" s="17" t="inlineStr">
         <is>
-          <t>43183</t>
+          <t>38430</t>
         </is>
       </c>
       <c r="C310" s="8" t="inlineStr">
         <is>
-          <t>Puerta Texcoco</t>
+          <t>Prisma Insurgentes</t>
         </is>
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
@@ -13965,17 +13965,17 @@
       </c>
       <c r="B311" s="15" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>43183</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>Punto MAQ</t>
+          <t>Puerta Texcoco</t>
         </is>
       </c>
       <c r="D311" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E311" s="11" t="n">
@@ -14005,17 +14005,17 @@
       </c>
       <c r="B312" s="17" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="C312" s="8" t="inlineStr">
         <is>
-          <t>Punto Polanco</t>
+          <t>Punto MAQ</t>
         </is>
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E312" s="7" t="n">
@@ -14045,17 +14045,17 @@
       </c>
       <c r="B313" s="15" t="inlineStr">
         <is>
-          <t>38654</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>Reforma 180</t>
+          <t>Punto Polanco</t>
         </is>
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E313" s="11" t="n">
@@ -14085,12 +14085,12 @@
       </c>
       <c r="B314" s="17" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>38654</t>
         </is>
       </c>
       <c r="C314" s="8" t="inlineStr">
         <is>
-          <t>Reforma 222</t>
+          <t>Reforma 180</t>
         </is>
       </c>
       <c r="D314" s="8" t="inlineStr">
@@ -14125,12 +14125,12 @@
       </c>
       <c r="B315" s="15" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>Reforma 222 II</t>
+          <t>Reforma 222</t>
         </is>
       </c>
       <c r="D315" s="12" t="inlineStr">
@@ -14165,17 +14165,17 @@
       </c>
       <c r="B316" s="17" t="inlineStr">
         <is>
-          <t>38560</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="C316" s="8" t="inlineStr">
         <is>
-          <t>Renato Leduc</t>
+          <t>Reforma 222 II</t>
         </is>
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E316" s="7" t="n">
@@ -14205,17 +14205,17 @@
       </c>
       <c r="B317" s="15" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>38560</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>Rio Hudson</t>
+          <t>Renato Leduc</t>
         </is>
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E317" s="11" t="n">
@@ -14245,17 +14245,17 @@
       </c>
       <c r="B318" s="17" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="C318" s="8" t="inlineStr">
         <is>
-          <t>Rio Marne</t>
+          <t>Rio Hudson</t>
         </is>
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
@@ -14285,17 +14285,17 @@
       </c>
       <c r="B319" s="15" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>Rio San Joaquin</t>
+          <t>Rio Marne</t>
         </is>
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E319" s="11" t="n">
@@ -14325,17 +14325,17 @@
       </c>
       <c r="B320" s="17" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="C320" s="8" t="inlineStr">
         <is>
-          <t>Rojo Gomez DT</t>
+          <t>Rio San Joaquin</t>
         </is>
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
+          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 18:12</t>
+          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -732,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1154,17 +1154,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Ariana Gutierrez</t>
+          <t>Monica Morales</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(D24/(D24+E24),0)</f>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Monica Morales</t>
+          <t>Ariana Gutierrez</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F25" s="13">
         <f>IFERROR(D25/(D25+E25),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
         </is>
       </c>
     </row>
@@ -2645,12 +2645,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>4</v>
@@ -2685,24 +2685,24 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
         <v>6</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin ll</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Ciudad Jardin ll</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6005,17 +6005,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6205,17 +6205,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6245,17 +6245,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6325,17 +6325,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6365,17 +6365,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -6565,17 +6565,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -6965,17 +6965,17 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
@@ -7085,17 +7085,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7125,17 +7125,17 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -7285,17 +7285,17 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
@@ -7445,17 +7445,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7605,17 +7605,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Plaza Oriente l</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Oriente l</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7685,17 +7685,17 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7765,17 +7765,17 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Rojo Gomez DT</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7805,17 +7805,17 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>43070</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Rojo Gomez DT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
@@ -7885,17 +7885,17 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8165,17 +8165,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8365,17 +8365,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8445,17 +8445,17 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
@@ -8485,17 +8485,17 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
@@ -8565,24 +8565,24 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>16 de Septiembre</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G176" s="9">
         <f>IFERROR(E176/(E176+F176),0)</f>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>5 de Mayo</t>
+          <t>16 de Septiembre</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
@@ -8645,17 +8645,17 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+          <t>5 de Mayo</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto D8</t>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Dufry</t>
+          <t>Aeropuerto D8</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto II Sala Bravo</t>
+          <t>Aeropuerto Dufry</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Aeropuerto Internacional II</t>
+          <t>Aeropuerto II Sala Bravo</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
@@ -8845,17 +8845,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Alfonso Reyes</t>
+          <t>Aeropuerto Internacional II</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8885,17 +8885,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38169</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Altavista</t>
+          <t>Alfonso Reyes</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8925,17 +8925,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Altavista</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9005,17 +9005,17 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9045,17 +9045,17 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
@@ -9085,17 +9085,17 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
@@ -9165,17 +9165,17 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
@@ -9365,17 +9365,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
@@ -9485,17 +9485,17 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
@@ -9525,17 +9525,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9565,17 +9565,17 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9605,17 +9605,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9845,17 +9845,17 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
@@ -9965,17 +9965,17 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16281,10 +16281,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 19:20</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -699,10 +699,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -2102,20 +2102,20 @@
         <v>8</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -2205,21 +2205,21 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>3</v>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2285,17 +2285,17 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:09</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -699,10 +699,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -2142,20 +2142,20 @@
         <v>8</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
         <v/>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -2245,21 +2245,21 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>3</v>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2525,17 +2525,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -2645,17 +2645,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>4</v>
@@ -2725,24 +2725,24 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:23</t>
+          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$361</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$121</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jarras'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
+          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3476</v>
+        <v>3471</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -732,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -798,10 +798,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
+          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
         </is>
       </c>
     </row>
@@ -2645,17 +2645,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>4</v>
@@ -2765,24 +2765,24 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
         <v>6</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2885,21 +2885,21 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>5</v>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>5</v>
@@ -2965,24 +2965,24 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -3005,17 +3005,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3845,24 +3845,24 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -3885,24 +3885,24 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G59" s="13">
         <f>IFERROR(E59/(E59+F59),0)</f>
@@ -3925,24 +3925,24 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -3965,17 +3965,17 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -4165,17 +4165,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
+          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16507,7 +16507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 20:53</t>
+          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
         </is>
       </c>
     </row>
@@ -17101,12 +17101,12 @@
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -17115,29 +17115,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-20%20at%208.13.27%20PM_Starbucks%20DT%20Perifer.jpeg</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -17146,29 +17146,29 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -17187,50 +17187,50 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -17239,29 +17239,29 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -17270,29 +17270,29 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -17301,29 +17301,29 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -17335,26 +17335,26 @@
         <v>1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -17363,29 +17363,29 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -17394,29 +17394,29 @@
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -17425,29 +17425,29 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -17466,19 +17466,19 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -17490,26 +17490,26 @@
         <v>2</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -17518,29 +17518,29 @@
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -17559,50 +17559,50 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -17621,19 +17621,19 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -17642,29 +17642,29 @@
         </is>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
         </is>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -17673,29 +17673,29 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -17707,26 +17707,26 @@
         <v>2</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -17745,19 +17745,19 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
         </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -17766,29 +17766,29 @@
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -17797,60 +17797,60 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -17869,19 +17869,19 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -17890,29 +17890,29 @@
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -17921,29 +17921,29 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -17952,29 +17952,29 @@
         </is>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -17983,29 +17983,29 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -18024,19 +18024,19 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -18055,19 +18055,19 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -18086,19 +18086,19 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -18117,19 +18117,19 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -18148,19 +18148,19 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -18172,57 +18172,57 @@
         <v>2</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D57" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -18231,29 +18231,29 @@
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -18262,29 +18262,29 @@
         </is>
       </c>
       <c r="D59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -18293,29 +18293,29 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -18327,26 +18327,26 @@
         <v>1</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891458560185071902259446244511_Starbucks%20La%20Provide.jpg</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -18355,29 +18355,29 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/f02dd0f0-5cfc-4765-8dee-2f6e56cc3966_Starbucks%20Metepec%20Pl%201.jpeg</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -18386,29 +18386,29 @@
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2724_Starbucks%20Pabell%C3%B3n%20M.jpeg</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -18427,19 +18427,19 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Paseo%20Toll.jpg</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
@@ -18451,26 +18451,26 @@
         <v>1</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890777852936622410369843650067_Starbucks%20Plaza%20Mayo.jpg</t>
         </is>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -18479,29 +18479,29 @@
         </is>
       </c>
       <c r="D66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Punta%20Zero.jpg</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -18510,34 +18510,34 @@
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789081729299746731757466114503_Starbucks%20Sendero%20To.jpg</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="D68" s="7" t="n">
@@ -18551,19 +18551,19 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Tecnologic.jpg</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -18572,29 +18572,29 @@
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="11" t="n">
         <v>2</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891490540425193622196681639535_Starbucks%20Ampliaci%C3%B3n.jpg</t>
         </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -18603,29 +18603,29 @@
         </is>
       </c>
       <c r="D70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891527872382285835886532009864_Starbucks%20M%C3%A9xico-Tol.jpg</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -18637,26 +18637,26 @@
         <v>1</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789160075772690215916016973008_Roberto%20Martinez%20Ava.jpg</t>
         </is>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -18665,29 +18665,29 @@
         </is>
       </c>
       <c r="D72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Castorena.jpg</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -18706,19 +18706,19 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891471261965215803384650122700_Starbucks%20Centro%20Com.jpg</t>
         </is>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -18737,19 +18737,19 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890773974875332894614468936668_Miriam%20Catharine%20Lop.jpg</t>
         </is>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -18768,19 +18768,19 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Melisa%20Moran%20Viveros.jpg</t>
         </is>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -18799,19 +18799,19 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/e0baec14-0005-4014-bb58-1d155b133fbe_Starbucks%20City%20Walk.jpeg</t>
         </is>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -18820,29 +18820,29 @@
         </is>
       </c>
       <c r="D77" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0045_Jaqueline%20Viridiana.jpg</t>
         </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
       <c r="A78" s="17" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -18861,19 +18861,19 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/9d66428d-428a-47eb-9662-764d3644e5bc_Francisco%20De%20Jesus%20C.jpeg</t>
         </is>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -18882,29 +18882,29 @@
         </is>
       </c>
       <c r="D79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443446617677037221249146333_Monica%20Luisa%20Baltaza.jpg</t>
         </is>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -18913,29 +18913,29 @@
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891533944206074033995426152966_Starbucks%20PATIO%20SANT.jpg</t>
         </is>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -18947,26 +18947,26 @@
         <v>1</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Fe.jpg</t>
         </is>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -18975,60 +18975,60 @@
         </is>
       </c>
       <c r="D82" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Ford%20Santa.jpg</t>
         </is>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Aeropuerto Toluca AMB</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="D83" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260911-WA0035_Starbucks%20Santa%20Fe%20I.jpg</t>
         </is>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Aeropuerto Toluca AMB</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -19047,19 +19047,19 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Apto%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -19068,29 +19068,29 @@
         </is>
       </c>
       <c r="D85" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_1565_Starbucks%20Apto%20Toluc.jpeg</t>
         </is>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -19109,19 +19109,19 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891477615931573389281316092983_Starbucks%20Centro%20M%C3%A9d.jpg</t>
         </is>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -19130,29 +19130,29 @@
         </is>
       </c>
       <c r="D87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891456981812662335160434415794_Jose%20Alejandro%20C%C3%A1rde.jpg</t>
         </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -19164,26 +19164,26 @@
         <v>2</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b5550aef-ef95-42a5-87b7-48dad9f3ad22_Starbucks%20Corporativ.jpeg</t>
         </is>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -19192,29 +19192,29 @@
         </is>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890772462346347401907392982370_Starbucks%20Garden%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -19223,29 +19223,29 @@
         </is>
       </c>
       <c r="D90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E90" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
         </is>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -19254,29 +19254,29 @@
         </is>
       </c>
       <c r="D91" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Parque%20la.jpg</t>
         </is>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -19295,19 +19295,19 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/51182c38-a448-4e8d-94b5-fcc391a86209_Starbucks%20Plaza%20Cent.jpeg</t>
         </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -19326,19 +19326,19 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1424eee3-897a-4119-99da-2a072368f0ac_Starbucks%20Plaza%20Lila.jpeg</t>
         </is>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -19347,29 +19347,29 @@
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891518600363903328021306956347_Starbucks%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -19378,29 +19378,29 @@
         </is>
       </c>
       <c r="D95" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E95" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20CC%20Samara.jpg</t>
         </is>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -19409,29 +19409,29 @@
         </is>
       </c>
       <c r="D96" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Superama%20S.jpg</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -19440,60 +19440,60 @@
         </is>
       </c>
       <c r="D97" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E97" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891457579454371302471952671937_Starbucks%20TEC%20SANTA.jpg</t>
         </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="D98" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E98" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F98" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891495890518840407956162909619_Starbucks%20TORRE%20ZENT.jpg</t>
         </is>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -19505,26 +19505,26 @@
         <v>2</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891484849447686090618664226870_Starbucks%20Av%20Coyoaca.jpg</t>
         </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -19543,19 +19543,19 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891487858866049755553381461545_Starbucks%20Felix%20Cuev.jpg</t>
         </is>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -19564,29 +19564,29 @@
         </is>
       </c>
       <c r="D101" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E101" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/03dfe0a9-ab71-471c-9f7c-f669e6d40145_Sharon%20Marely%20Piedra.jpeg</t>
         </is>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -19595,29 +19595,29 @@
         </is>
       </c>
       <c r="D102" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-11%20at%2011.14.49_Ana%20Katherina%20Velazq.jpeg</t>
         </is>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -19636,19 +19636,19 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3bacf93e-9eca-4679-9f2d-920e1b37f5c4_Starbucks%20Metropoli.jpeg</t>
         </is>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
@@ -19660,26 +19660,26 @@
         <v>2</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/d6478724-30e8-4031-a680-4bed81089e3e_Heidi%20Laura%20Garcia%20G.jpeg</t>
         </is>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -19688,29 +19688,29 @@
         </is>
       </c>
       <c r="D105" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/68de3cea-5d8e-4bc0-8be6-fac972f096a9_Diana%20Patricia%20Arias.jpeg</t>
         </is>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -19719,29 +19719,29 @@
         </is>
       </c>
       <c r="D106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E106" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Maria%20Fernanda%20Migue.jpg</t>
         </is>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Universidad Panamericana</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -19760,50 +19760,50 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891548823645550132900060579449_Starbucks%20Plateros.jpg</t>
         </is>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="D108" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E108" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F108" s="7" t="n">
-        <v>6</v>
-      </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891454523977582754072023932885_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -19812,29 +19812,29 @@
         </is>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/978863c9-7393-4493-bdb8-b2b7142e38e3_Maria%20Teresa%20Espinoz.jpeg</t>
         </is>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
@@ -19846,26 +19846,26 @@
         <v>1</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/b78876df-36ce-4085-a680-6177919ca771_Carlos%20Rodriguez%20Mor.jpeg</t>
         </is>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -19874,29 +19874,29 @@
         </is>
       </c>
       <c r="D111" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Naomi%20Arlene%20Orozco.jpg</t>
         </is>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -19905,29 +19905,29 @@
         </is>
       </c>
       <c r="D112" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0143_Starbucks%20Corporativ.jpg</t>
         </is>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -19936,29 +19936,29 @@
         </is>
       </c>
       <c r="D113" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E113" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260912-WA0002_Starbucks%20Parque%20Dur.jpg</t>
         </is>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -19977,19 +19977,19 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890771429977242503454425821765_Starbucks%20Fuente%20de.jpg</t>
         </is>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -19998,29 +19998,29 @@
         </is>
       </c>
       <c r="D115" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890790939377071165929558693206_Fernando%20Axel%20Velasc.jpg</t>
         </is>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -20029,29 +20029,29 @@
         </is>
       </c>
       <c r="D116" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E116" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890779419685586202685537762_Starbucks%20Hospital%20A.jpg</t>
         </is>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -20060,29 +20060,29 @@
         </is>
       </c>
       <c r="D117" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E117" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Monte%20Pelv.jpg</t>
         </is>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
       <c r="A118" s="17" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -20094,26 +20094,26 @@
         <v>2</v>
       </c>
       <c r="E118" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Eduardo%20Hernandez%20Pe.jpg</t>
         </is>
       </c>
     </row>
     <row r="119" ht="21" customHeight="1">
       <c r="A119" s="15" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -20132,19 +20132,19 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891443650005481224244539957154_Starbucks%20Portal%20San.jpg</t>
         </is>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
       <c r="A120" s="17" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
@@ -20156,41 +20156,72 @@
         <v>2</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_155344172_HDR_Starbucks%20Portal%20San.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="21" customHeight="1">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>38644</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Torre Virreyes</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G120" s="8" t="inlineStr">
+      <c r="G121" s="12" t="inlineStr">
         <is>
           <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891464434056746458223120183687_Starbucks%20Torre%20Virr.jpg</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="21" customHeight="1">
-      <c r="A121" s="18" t="n"/>
-      <c r="B121" s="19" t="n"/>
-      <c r="C121" s="19" t="inlineStr">
+    <row r="122" ht="21" customHeight="1">
+      <c r="A122" s="18" t="n"/>
+      <c r="B122" s="19" t="n"/>
+      <c r="C122" s="19" t="inlineStr">
         <is>
           <t>Consolidado</t>
         </is>
       </c>
-      <c r="D121" s="20">
-        <f>SUM(D5:D120)</f>
-        <v/>
-      </c>
-      <c r="E121" s="20">
-        <f>SUM(E5:E120)</f>
-        <v/>
-      </c>
-      <c r="F121" s="20">
-        <f>SUM(F5:F120)</f>
-        <v/>
-      </c>
-      <c r="G121" s="19" t="n"/>
+      <c r="D122" s="20">
+        <f>SUM(D5:D121)</f>
+        <v/>
+      </c>
+      <c r="E122" s="20">
+        <f>SUM(E5:E121)</f>
+        <v/>
+      </c>
+      <c r="F122" s="20">
+        <f>SUM(F5:F121)</f>
+        <v/>
+      </c>
+      <c r="G122" s="19" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G120"/>
+  <autoFilter ref="A4:G121"/>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:G2"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
+          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
+          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
         </is>
       </c>
     </row>
@@ -3045,37 +3045,37 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
         <v/>
       </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3085,12 +3085,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -3125,12 +3125,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -3205,24 +3205,24 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3285,24 +3285,24 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3805,17 +3805,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3925,24 +3925,24 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
+          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
         </is>
       </c>
     </row>
@@ -16106,10 +16106,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 20/09/2026 23:47</t>
+          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$361</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jarras'!$A$4:$G$122</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jarras'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
+          <t>Todas las regiones · Corte 21/09/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -633,10 +633,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3469</v>
+        <v>3466</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -732,10 +732,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1668,7 +1668,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
+          <t>Todas las regiones · Corte 21/09/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1845,17 +1845,17 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1965,21 +1965,21 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>2</v>
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2182,20 +2182,20 @@
         <v>8</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
         <v/>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2205,17 +2205,17 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2285,21 +2285,21 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>3</v>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>3</v>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -2382,7 +2382,7 @@
         <v>7</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
         <v>7</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -16050,7 +16050,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
+          <t>Todas las regiones · Corte 21/09/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -16211,10 +16211,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16421,10 +16421,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16507,7 +16507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16530,7 +16530,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 21/09/2026 06:23</t>
+          <t>Todas las regiones · Corte 21/09/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -17070,12 +17070,12 @@
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -17084,29 +17084,29 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/DCE3998D-8289-4330-B730-ED55D6A2A656_Starbucks%20Gustavo%20Ba.jpeg</t>
         </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -17115,29 +17115,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-20%20at%208.13.27%20PM_Starbucks%20DT%20Perifer.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -17146,29 +17146,29 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-20%20at%208.13.27%20PM_Starbucks%20DT%20Perifer.jpeg</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -17177,29 +17177,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Plaza%20Sate.jpg</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -17218,50 +17218,50 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/8f52f589-d349-40ed-8988-aa0965929338_Starbucks%20Satelite.jpeg</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Aguilas</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Aguilas</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -17270,29 +17270,29 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891757480322115482528748859301_Starbucks%20Aguilas.jpg</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -17301,29 +17301,29 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Alberto%20Medina%20Magda.jpg</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -17332,29 +17332,29 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Axomiatla.jpg</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -17366,26 +17366,26 @@
         <v>1</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891289060857418363167355556294_Luis%20Javer%20Romo%20de%20V.jpg</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -17394,29 +17394,29 @@
         </is>
       </c>
       <c r="D31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260910_175237_Starbucks%20Parroquia.jpg</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -17425,29 +17425,29 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17891450105013340269761926142251_Starbucks%20Lomas%20Plaz.jpg</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -17456,29 +17456,29 @@
         </is>
       </c>
       <c r="D33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0550_Starbucks%20Manacar%20PB.jpeg</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -17497,19 +17497,19 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/201e0550-6732-4c0b-99a0-3f08ae95a6a5_Starbucks%20Montes%20Ura.jpeg</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -17521,26 +17521,26 @@
         <v>2</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-10%20at%2018.54.34_Laura%20Gonzalez%20Saave.jpeg</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -17549,29 +17549,29 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_0485_Starbucks%20Plaza%20Exhi.jpeg</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Universidad Anahuac Campus Sur</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -17590,50 +17590,50 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Prado%20Nort.jpg</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -17652,19 +17652,19 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carretera.jpg</t>
         </is>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -17673,29 +17673,29 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789146696974620872336528797371_Starbucks%20Col%C3%B3n%20Casa.jpg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
@@ -17704,29 +17704,29 @@
         </is>
       </c>
       <c r="D41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1789162797581621059248875744315_Starbucks%20El%20Molino.jpg</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -17738,26 +17738,26 @@
         <v>2</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3b0fab7e-3218-44ae-afb5-aac017f62aa5_Starbucks%20Galerias%20T.jpeg</t>
         </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -17776,19 +17776,19 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Cassandra%20Victoria%20F.jpg</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -17797,29 +17797,29 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG20260911115238_Starbucks%20Outlet%20Ler.jpg</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -17828,60 +17828,60 @@
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Patio%20Tolu.jpg</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/45d13dfb-8534-443b-b50d-4597cc831776_Jorge%20Humberto%20Rojas.jpeg</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
@@ -17900,19 +17900,19 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890918167577646536806356657923_Starbucks%20Av%20Stim.jpg</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -17921,29 +17921,29 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0005_Starbucks%20Bosque%20Rea.jpeg</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -17952,29 +17952,29 @@
         </is>
       </c>
       <c r="D49" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>3</v>
-      </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0038_Starbucks%20Central%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -17983,29 +17983,29 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890778184532045965930032790920_Starbucks%20Jesus%20Del.jpg</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -18014,29 +18014,29 @@
         </is>
       </c>
       <c r="D51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/jarras_Starbucks%20Magnocentr.jpg</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -18055,19 +18055,19 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_7022_Alison%20Ariadna%20De%20La.jpeg</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
@@ -18086,19 +18086,19 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/743dc6cd-2b48-47f6-8758-ac5f8887a000_Moises%20Garcia%20Santos.jpeg</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -18117,19 +18117,19 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monserrat%20Soriano%20Es.jpg</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -18148,19 +18148,19 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Universidad Anáhuac</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -18179,19 +18179,19 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890816102755265318990470575210_Starbucks%20Paseo%20Inte.jpg</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Ángeles Interlomas</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -18203,57 +18203,57 @@
         <v>2</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890806432661412731394071096776_Starbucks%20Universida.jpg</t>
         </is>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17890799629012418616368564720381_Starbucks%20Angeles%20In.jpg</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -18262,29 +18262,29 @@
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260911_134342556_HDR_Starbucks%20Avandaro.jpg</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -18293,29 +18293,29 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260910-WA0086_Francisco%20Manuel%20Gon.jpg</t>
+          <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Carr%20Toluc.jpg</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>43068</t>
         </i